--- a/results/table/28_kor_share_vs_exposure.xlsx
+++ b/results/table/28_kor_share_vs_exposure.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="652">
   <si>
     <t>KSCO 8차 소분류</t>
   </si>
@@ -359,39 +359,39 @@
     <t>441</t>
   </si>
   <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>433</t>
+  </si>
+  <si>
+    <t>751</t>
+  </si>
+  <si>
+    <t>429</t>
+  </si>
+  <si>
+    <t>613</t>
+  </si>
+  <si>
     <t>843</t>
   </si>
   <si>
-    <t>238</t>
-  </si>
-  <si>
-    <t>433</t>
-  </si>
-  <si>
-    <t>751</t>
-  </si>
-  <si>
-    <t>429</t>
-  </si>
-  <si>
-    <t>613</t>
+    <t>872</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>871</t>
+  </si>
+  <si>
+    <t>873</t>
   </si>
   <si>
     <t>864</t>
   </si>
   <si>
-    <t>872</t>
-  </si>
-  <si>
-    <t>252</t>
-  </si>
-  <si>
-    <t>871</t>
-  </si>
-  <si>
-    <t>873</t>
-  </si>
-  <si>
     <t>922</t>
   </si>
   <si>
@@ -749,39 +749,39 @@
     <t>운송 서비스 종사자</t>
   </si>
   <si>
+    <t>항공기‧선박 기관사 및 관제사</t>
+  </si>
+  <si>
+    <t>동물 관련 서비스 종사자</t>
+  </si>
+  <si>
+    <t>자동차 정비원</t>
+  </si>
+  <si>
+    <t>기타 돌봄 및 보건 서비스 종사자</t>
+  </si>
+  <si>
+    <t>축산 및 사육 관련 종사자</t>
+  </si>
+  <si>
     <t>비금속제품 생산기 조작원</t>
   </si>
   <si>
-    <t>항공기‧선박 기관사 및 관제사</t>
-  </si>
-  <si>
-    <t>동물 관련 서비스 종사자</t>
-  </si>
-  <si>
-    <t>자동차 정비원</t>
-  </si>
-  <si>
-    <t>기타 돌봄 및 보건 서비스 종사자</t>
-  </si>
-  <si>
-    <t>축산 및 사육 관련 종사자</t>
+    <t>자동차 운전원</t>
+  </si>
+  <si>
+    <t>시민사회 활동가</t>
+  </si>
+  <si>
+    <t>철도‧전동차 기관사 및 관련 종사자</t>
+  </si>
+  <si>
+    <t>물품 이동 장비 조작원</t>
   </si>
   <si>
     <t>전기‧전자 부품 및 제품 조립원</t>
   </si>
   <si>
-    <t>자동차 운전원</t>
-  </si>
-  <si>
-    <t>시민사회 활동가</t>
-  </si>
-  <si>
-    <t>철도‧전동차 기관사 및 관련 종사자</t>
-  </si>
-  <si>
-    <t>물품 이동 장비 조작원</t>
-  </si>
-  <si>
     <t>배달원</t>
   </si>
   <si>
@@ -1064,45 +1064,42 @@
     <t>4</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>대분류 명칭</t>
   </si>
   <si>
@@ -1365,9 +1362,6 @@
   </si>
   <si>
     <t>서비스 종사자</t>
-  </si>
-  <si>
-    <t>장치∙기계 조작 및 조립 종사자</t>
   </si>
   <si>
     <t>전문가 및 관련 종사자</t>
@@ -2039,58 +2033,58 @@
         <v>260</v>
       </c>
       <c r="D1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E1" t="s">
+        <v>460</v>
+      </c>
+      <c r="F1" t="s">
+        <v>461</v>
+      </c>
+      <c r="G1" t="s">
         <v>462</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>463</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>464</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>465</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>466</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>467</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>468</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>469</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>470</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>471</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>472</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>473</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>474</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>475</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>476</v>
-      </c>
-      <c r="T1" t="s">
-        <v>477</v>
-      </c>
-      <c r="U1" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="2">
@@ -2104,16 +2098,16 @@
         <v>261</v>
       </c>
       <c r="D2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E2" s="1">
-        <v>9.9489956082449442</v>
+        <v>9.951642740971387</v>
       </c>
       <c r="F2" s="1">
-        <v>12.205055216602284</v>
+        <v>12.205793816401675</v>
       </c>
       <c r="G2" s="1">
-        <v>11.555648251813194</v>
+        <v>11.556294251698699</v>
       </c>
       <c r="H2" s="1">
         <v>0.40150381944444441</v>
@@ -2169,16 +2163,16 @@
         <v>261</v>
       </c>
       <c r="D3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E3" s="1">
-        <v>11.919083748493749</v>
+        <v>11.922160835717158</v>
       </c>
       <c r="F3" s="1">
-        <v>10.470620398002232</v>
+        <v>10.470864959921744</v>
       </c>
       <c r="G3" s="1">
-        <v>11.08026246511187</v>
+        <v>11.080470160565543</v>
       </c>
       <c r="H3" s="1">
         <v>0.27601250000000005</v>
@@ -2234,31 +2228,31 @@
         <v>262</v>
       </c>
       <c r="D4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E4" s="1">
-        <v>4.6909595762652279</v>
+        <v>4.6921112119957229</v>
       </c>
       <c r="F4" s="1">
-        <v>5.2381965046843524</v>
+        <v>5.2381035736532535</v>
       </c>
       <c r="G4" s="1">
-        <v>5.8059563107367413</v>
+        <v>5.8058265291582698</v>
       </c>
       <c r="H4" s="1">
-        <v>0.22829700374531839</v>
+        <v>0.22829700374531836</v>
       </c>
       <c r="I4" s="1">
-        <v>0.66290078296296306</v>
+        <v>0.66290078296296295</v>
       </c>
       <c r="J4" s="1">
-        <v>0.6313545494757945</v>
+        <v>0.63135454947579439</v>
       </c>
       <c r="K4" s="1">
-        <v>3.7357568806771941</v>
+        <v>3.7357568806771937</v>
       </c>
       <c r="L4" s="1">
-        <v>2.5926077111509271</v>
+        <v>2.5926077111509267</v>
       </c>
       <c r="M4" s="1">
         <v>4</v>
@@ -2299,16 +2293,16 @@
         <v>263</v>
       </c>
       <c r="D5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E5" s="1">
-        <v>8.3138712982458056</v>
+        <v>8.3161809478554503</v>
       </c>
       <c r="F5" s="1">
-        <v>5.3352819759573293</v>
+        <v>5.33563124058578</v>
       </c>
       <c r="G5" s="1">
-        <v>5.1326764864572665</v>
+        <v>5.1329888132748298</v>
       </c>
       <c r="H5" s="1">
         <v>0.35310833333333341</v>
@@ -2364,16 +2358,16 @@
         <v>263</v>
       </c>
       <c r="D6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E6" s="1">
-        <v>4.1979989332147127</v>
+        <v>4.1991845684272011</v>
       </c>
       <c r="F6" s="1">
-        <v>5.1457592226878637</v>
+        <v>5.1463389598411275</v>
       </c>
       <c r="G6" s="1">
-        <v>5.055755116928899</v>
+        <v>5.0563013930351088</v>
       </c>
       <c r="H6" s="1">
         <v>0.35134900000000002</v>
@@ -2429,31 +2423,31 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E7" s="1">
-        <v>2.6125334323034219</v>
+        <v>2.6131883931440973</v>
       </c>
       <c r="F7" s="1">
-        <v>4.0275593292344318</v>
+        <v>4.0275728147760459</v>
       </c>
       <c r="G7" s="1">
-        <v>4.1950389570438817</v>
+        <v>4.1950336548328799</v>
       </c>
       <c r="H7" s="1">
-        <v>0.29911739130434783</v>
+        <v>0.29911739130434778</v>
       </c>
       <c r="I7" s="1">
-        <v>1.2524687303370787</v>
+        <v>1.2524687303370785</v>
       </c>
       <c r="J7" s="1">
-        <v>0.78679594367835848</v>
+        <v>0.78679594367835837</v>
       </c>
       <c r="K7" s="1">
-        <v>0.22115817067440369</v>
+        <v>0.22115817067440363</v>
       </c>
       <c r="L7" s="1">
-        <v>0.14598510194095085</v>
+        <v>0.14598510194095082</v>
       </c>
       <c r="M7" s="1">
         <v>9</v>
@@ -2494,28 +2488,28 @@
         <v>265</v>
       </c>
       <c r="D8" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E8" s="1">
-        <v>2.7860580371360091</v>
+        <v>2.7867852169946694</v>
       </c>
       <c r="F8" s="1">
-        <v>3.6156087412437614</v>
+        <v>3.6157023832904631</v>
       </c>
       <c r="G8" s="1">
-        <v>3.5074137479836272</v>
+        <v>3.5074884104469102</v>
       </c>
       <c r="H8" s="1">
-        <v>0.12869727626459149</v>
+        <v>0.12869727626459143</v>
       </c>
       <c r="I8" s="1">
-        <v>-0.068931373333333379</v>
+        <v>-0.068931373333333365</v>
       </c>
       <c r="J8" s="1">
         <v>0.44179620692135796</v>
       </c>
       <c r="K8" s="1">
-        <v>0.068839113662958876</v>
+        <v>0.068839113662958834</v>
       </c>
       <c r="L8" s="1">
         <v>0.059302499421543857</v>
@@ -2559,16 +2553,16 @@
         <v>265</v>
       </c>
       <c r="D9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E9" s="1">
-        <v>3.8377186980814013</v>
+        <v>3.8387231037481451</v>
       </c>
       <c r="F9" s="1">
-        <v>3.7443605397263893</v>
+        <v>3.7445294289172639</v>
       </c>
       <c r="G9" s="1">
-        <v>3.5058879772531526</v>
+        <v>3.5060299394785881</v>
       </c>
       <c r="H9" s="1">
         <v>0.38766428571428574</v>
@@ -2624,31 +2618,31 @@
         <v>265</v>
       </c>
       <c r="D10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E10" s="1">
-        <v>2.4265848178966718</v>
+        <v>2.4271760759805621</v>
       </c>
       <c r="F10" s="1">
-        <v>2.847400806210596</v>
+        <v>2.8474185842697111</v>
       </c>
       <c r="G10" s="1">
-        <v>2.9143975934326551</v>
+        <v>2.9144023478528807</v>
       </c>
       <c r="H10" s="1">
         <v>0.069515789473684197</v>
       </c>
       <c r="I10" s="1">
-        <v>0.32138106351351348</v>
+        <v>0.32138106351351353</v>
       </c>
       <c r="J10" s="1">
-        <v>0.39244098571824793</v>
+        <v>0.39244098571824787</v>
       </c>
       <c r="K10" s="1">
         <v>0.38708945914276854</v>
       </c>
       <c r="L10" s="1">
-        <v>0.54838724450431131</v>
+        <v>0.5483872445043112</v>
       </c>
       <c r="M10" s="1">
         <v>11</v>
@@ -2689,31 +2683,31 @@
         <v>265</v>
       </c>
       <c r="D11" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E11" s="1">
-        <v>2.0440927051250171</v>
+        <v>2.0446758645434997</v>
       </c>
       <c r="F11" s="1">
-        <v>2.8876554380861652</v>
+        <v>2.8878725943338863</v>
       </c>
       <c r="G11" s="1">
-        <v>2.7840544617143244</v>
+        <v>2.7842509853544963</v>
       </c>
       <c r="H11" s="1">
-        <v>0.09777830508474572</v>
+        <v>0.097778305084745748</v>
       </c>
       <c r="I11" s="1">
-        <v>0.74346233898305047</v>
+        <v>0.7434623389830507</v>
       </c>
       <c r="J11" s="1">
-        <v>0.4930939170076693</v>
+        <v>0.49309391700766941</v>
       </c>
       <c r="K11" s="1">
-        <v>0.34650418060399518</v>
+        <v>0.34650418060399524</v>
       </c>
       <c r="L11" s="1">
-        <v>0.43851122982481022</v>
+        <v>0.43851122982481033</v>
       </c>
       <c r="M11" s="1">
         <v>12</v>
@@ -2754,16 +2748,16 @@
         <v>265</v>
       </c>
       <c r="D12" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E12" s="1">
-        <v>1.8522079257318833</v>
+        <v>1.8528466500995548</v>
       </c>
       <c r="F12" s="1">
-        <v>2.0654243923461149</v>
+        <v>2.0661648211365025</v>
       </c>
       <c r="G12" s="1">
-        <v>2.7368028789218206</v>
+        <v>2.7377713612204535</v>
       </c>
       <c r="H12" s="1">
         <v>0.11025978260869565</v>
@@ -2772,13 +2766,13 @@
         <v>0.91929314705882348</v>
       </c>
       <c r="J12" s="1">
-        <v>0.39950365462677806</v>
+        <v>0.39950365462677795</v>
       </c>
       <c r="K12" s="1">
         <v>3.0025148632540031</v>
       </c>
       <c r="L12" s="1">
-        <v>2.7300706836664372</v>
+        <v>2.7300706836664368</v>
       </c>
       <c r="M12" s="1">
         <v>14</v>
@@ -2819,16 +2813,16 @@
         <v>265</v>
       </c>
       <c r="D13" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E13" s="1">
-        <v>3.8076763056984682</v>
+        <v>3.8084736350403889</v>
       </c>
       <c r="F13" s="1">
-        <v>2.2864475208325361</v>
+        <v>2.2861073218643599</v>
       </c>
       <c r="G13" s="1">
-        <v>2.368713428897923</v>
+        <v>2.3683500662281531</v>
       </c>
       <c r="H13" s="1">
         <v>0.17897916666666669</v>
@@ -2884,28 +2878,28 @@
         <v>265</v>
       </c>
       <c r="D14" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E14" s="1">
-        <v>1.4114108610759752</v>
+        <v>1.4118244192159439</v>
       </c>
       <c r="F14" s="1">
-        <v>2.0216175474699516</v>
+        <v>2.0219045481785898</v>
       </c>
       <c r="G14" s="1">
-        <v>2.3277900736984605</v>
+        <v>2.3281098026431737</v>
       </c>
       <c r="H14" s="1">
-        <v>0.21488969849246228</v>
+        <v>0.2148896984924622</v>
       </c>
       <c r="I14" s="1">
-        <v>1.4009040241379305</v>
+        <v>1.4009040241379302</v>
       </c>
       <c r="J14" s="1">
         <v>0.45729448035298598</v>
       </c>
       <c r="K14" s="1">
-        <v>0.45757634184961399</v>
+        <v>0.45757634184961371</v>
       </c>
       <c r="L14" s="1">
         <v>0.24435938621056139</v>
@@ -2949,25 +2943,25 @@
         <v>265</v>
       </c>
       <c r="D15" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E15" s="1">
-        <v>1.9835061379750201</v>
+        <v>1.9840277036507501</v>
       </c>
       <c r="F15" s="1">
-        <v>2.4817983808640602</v>
+        <v>2.4817536901249335</v>
       </c>
       <c r="G15" s="1">
-        <v>2.3016561939632507</v>
+        <v>2.301604131552224</v>
       </c>
       <c r="H15" s="1">
         <v>0.2693208823529411</v>
       </c>
       <c r="I15" s="1">
-        <v>1.1775599840277777</v>
+        <v>1.1775599840277775</v>
       </c>
       <c r="J15" s="1">
-        <v>0.53344181395474199</v>
+        <v>0.53344181395474188</v>
       </c>
       <c r="K15" s="1">
         <v>0.59161703946604083</v>
@@ -3014,19 +3008,19 @@
         <v>266</v>
       </c>
       <c r="D16" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E16" s="1">
-        <v>2.6104749290920299</v>
+        <v>2.6110528514292355</v>
       </c>
       <c r="F16" s="1">
-        <v>1.7779609147635014</v>
+        <v>1.7777615079702584</v>
       </c>
       <c r="G16" s="1">
-        <v>1.7280500285695066</v>
+        <v>1.7278482502588635</v>
       </c>
       <c r="H16" s="1">
-        <v>0.1375597014925373</v>
+        <v>0.13755970149253727</v>
       </c>
       <c r="I16" s="1">
         <v>1.0947411940298506</v>
@@ -3035,7 +3029,7 @@
         <v>0.59873874398128135</v>
       </c>
       <c r="K16" s="1">
-        <v>1.8378091533739533</v>
+        <v>1.8378091533739531</v>
       </c>
       <c r="L16" s="1">
         <v>2.0073895003766764</v>
@@ -3079,16 +3073,16 @@
         <v>267</v>
       </c>
       <c r="D17" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E17" s="1">
-        <v>1.0984227637495725</v>
+        <v>1.0987265690894208</v>
       </c>
       <c r="F17" s="1">
-        <v>1.8198186612449911</v>
+        <v>1.8200032248100204</v>
       </c>
       <c r="G17" s="1">
-        <v>1.7170070853750834</v>
+        <v>1.7171733019023854</v>
       </c>
       <c r="H17" s="1">
         <v>0.4551</v>
@@ -3144,19 +3138,19 @@
         <v>267</v>
       </c>
       <c r="D18" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E18" s="1">
-        <v>1.7051886754863237</v>
+        <v>1.7056512357400035</v>
       </c>
       <c r="F18" s="1">
-        <v>1.6988461889477637</v>
+        <v>1.6989349981503663</v>
       </c>
       <c r="G18" s="1">
-        <v>1.5911404952949033</v>
+        <v>1.591216334973192</v>
       </c>
       <c r="H18" s="1">
-        <v>0.034012121212121209</v>
+        <v>0.034012121212121202</v>
       </c>
       <c r="I18" s="1">
         <v>0.48729186583333339</v>
@@ -3165,7 +3159,7 @@
         <v>0.47058741195926262</v>
       </c>
       <c r="K18" s="1">
-        <v>0.19380514598165685</v>
+        <v>0.1938051459816568</v>
       </c>
       <c r="L18" s="1">
         <v>0.67291001625130487</v>
@@ -3209,16 +3203,16 @@
         <v>268</v>
       </c>
       <c r="D19" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E19" s="1">
-        <v>1.0103248811908387</v>
+        <v>1.0106094109784591</v>
       </c>
       <c r="F19" s="1">
-        <v>1.5007682606369694</v>
+        <v>1.5009496004151772</v>
       </c>
       <c r="G19" s="1">
-        <v>1.4407456594950288</v>
+        <v>1.4409131008186427</v>
       </c>
       <c r="H19" s="1">
         <v>0.18618571428571432</v>
@@ -3274,31 +3268,31 @@
         <v>269</v>
       </c>
       <c r="D20" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E20" s="1">
-        <v>1.0095757252968496</v>
+        <v>1.0098706628616125</v>
       </c>
       <c r="F20" s="1">
-        <v>1.11539858331807</v>
+        <v>1.1155532282604517</v>
       </c>
       <c r="G20" s="1">
-        <v>1.3256574972945001</v>
+        <v>1.325835178601309</v>
       </c>
       <c r="H20" s="1">
         <v>0.13179428571428584</v>
       </c>
       <c r="I20" s="1">
-        <v>1.5244266285714299</v>
+        <v>1.5244266285714294</v>
       </c>
       <c r="J20" s="1">
-        <v>0.48574729457093235</v>
+        <v>0.4857472945709323</v>
       </c>
       <c r="K20" s="1">
         <v>0.69642239431398401</v>
       </c>
       <c r="L20" s="1">
-        <v>0.64412719947974617</v>
+        <v>0.64412719947974606</v>
       </c>
       <c r="M20" s="1">
         <v>26</v>
@@ -3339,16 +3333,16 @@
         <v>270</v>
       </c>
       <c r="D21" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E21" s="1">
-        <v>1.3851892258083494</v>
+        <v>1.3855607836352899</v>
       </c>
       <c r="F21" s="1">
-        <v>1.349543596126598</v>
+        <v>1.3496412902737855</v>
       </c>
       <c r="G21" s="1">
-        <v>1.2845731910637455</v>
+        <v>1.284660256801095</v>
       </c>
       <c r="H21" s="1">
         <v>0.06146153846153847</v>
@@ -3357,13 +3351,13 @@
         <v>0.99693992777777773</v>
       </c>
       <c r="J21" s="1">
-        <v>0.46273946032675445</v>
+        <v>0.46273946032675461</v>
       </c>
       <c r="K21" s="1">
         <v>0.14442324350542843</v>
       </c>
       <c r="L21" s="1">
-        <v>0.27286969396669181</v>
+        <v>0.27286969396669192</v>
       </c>
       <c r="M21" s="1">
         <v>17</v>
@@ -3404,22 +3398,22 @@
         <v>271</v>
       </c>
       <c r="D22" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E22" s="1">
-        <v>1.0693294444207642</v>
+        <v>1.0696006694162525</v>
       </c>
       <c r="F22" s="1">
-        <v>1.3300824168231886</v>
+        <v>1.3300787285855828</v>
       </c>
       <c r="G22" s="1">
-        <v>1.2561153622225756</v>
+        <v>1.2561060856207971</v>
       </c>
       <c r="H22" s="1">
         <v>0.040463513513513523</v>
       </c>
       <c r="I22" s="1">
-        <v>0.34573607758620695</v>
+        <v>0.34573607758620684</v>
       </c>
       <c r="J22" s="1">
         <v>0.45791075985945801</v>
@@ -3469,31 +3463,31 @@
         <v>272</v>
       </c>
       <c r="D23" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E23" s="1">
-        <v>0.86826408679406097</v>
+        <v>0.86849594217852155</v>
       </c>
       <c r="F23" s="1">
-        <v>1.3231618854087233</v>
+        <v>1.3232369579042118</v>
       </c>
       <c r="G23" s="1">
-        <v>1.2467859109330286</v>
+        <v>1.2468508992867511</v>
       </c>
       <c r="H23" s="1">
-        <v>0.15592343749999998</v>
+        <v>0.15592343750000001</v>
       </c>
       <c r="I23" s="1">
         <v>1.0298459697916664</v>
       </c>
       <c r="J23" s="1">
-        <v>0.47282892980551228</v>
+        <v>0.47282892980551222</v>
       </c>
       <c r="K23" s="1">
-        <v>0.44205407709191752</v>
+        <v>0.44205407709191763</v>
       </c>
       <c r="L23" s="1">
-        <v>0.33639779565914307</v>
+        <v>0.33639779565914302</v>
       </c>
       <c r="M23" s="1">
         <v>29</v>
@@ -3534,28 +3528,28 @@
         <v>273</v>
       </c>
       <c r="D24" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E24" s="1">
-        <v>1.0363963843419679</v>
+        <v>1.0366298733644961</v>
       </c>
       <c r="F24" s="1">
-        <v>1.2517941610943224</v>
+        <v>1.2516704533261991</v>
       </c>
       <c r="G24" s="1">
-        <v>1.1890628033336259</v>
+        <v>1.1889398112694201</v>
       </c>
       <c r="H24" s="1">
-        <v>0.18975514705882349</v>
+        <v>0.18975514705882354</v>
       </c>
       <c r="I24" s="1">
-        <v>1.4219850161764702</v>
+        <v>1.4219850161764704</v>
       </c>
       <c r="J24" s="1">
         <v>0.44940999388261055</v>
       </c>
       <c r="K24" s="1">
-        <v>0.28972576846378945</v>
+        <v>0.2897257684637895</v>
       </c>
       <c r="L24" s="1">
         <v>0.17219533644717777</v>
@@ -3599,28 +3593,28 @@
         <v>273</v>
       </c>
       <c r="D25" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E25" s="1">
-        <v>1.2640360145591758</v>
+        <v>1.2643460247548917</v>
       </c>
       <c r="F25" s="1">
-        <v>1.122029741202607</v>
+        <v>1.1219831505397928</v>
       </c>
       <c r="G25" s="1">
-        <v>1.1504763137262528</v>
+        <v>1.1504232358256326</v>
       </c>
       <c r="H25" s="1">
-        <v>0.17877777777777779</v>
+        <v>0.17877777777777776</v>
       </c>
       <c r="I25" s="1">
-        <v>1.3664642666666666</v>
+        <v>1.3664642666666669</v>
       </c>
       <c r="J25" s="1">
-        <v>0.49392925779282271</v>
+        <v>0.49392925779282276</v>
       </c>
       <c r="K25" s="1">
-        <v>0.18148126454994068</v>
+        <v>0.18148126454994065</v>
       </c>
       <c r="L25" s="1">
         <v>0.12582534072874491</v>
@@ -3664,16 +3658,16 @@
         <v>274</v>
       </c>
       <c r="D26" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E26" s="1">
-        <v>1.3305896633377174</v>
+        <v>1.3309437331362211</v>
       </c>
       <c r="F26" s="1">
-        <v>1.008265871997162</v>
+        <v>1.0083065524583175</v>
       </c>
       <c r="G26" s="1">
-        <v>0.99371876641788459</v>
+        <v>0.99375427650835435</v>
       </c>
       <c r="H26" s="1">
         <v>0.26629999999999998</v>
@@ -3729,28 +3723,28 @@
         <v>275</v>
       </c>
       <c r="D27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E27" s="1">
-        <v>1.1907102755202106</v>
+        <v>1.191052110120328</v>
       </c>
       <c r="F27" s="1">
-        <v>1.0121064553919348</v>
+        <v>1.012201448219201</v>
       </c>
       <c r="G27" s="1">
-        <v>0.99305408646041382</v>
+        <v>0.99314271047939906</v>
       </c>
       <c r="H27" s="1">
-        <v>0.15047400000000002</v>
+        <v>0.150474</v>
       </c>
       <c r="I27" s="1">
-        <v>0.38032101799999996</v>
+        <v>0.38032101800000001</v>
       </c>
       <c r="J27" s="1">
         <v>0.45142304000438804</v>
       </c>
       <c r="K27" s="1">
-        <v>1.8669340748310868</v>
+        <v>1.8669340748310863</v>
       </c>
       <c r="L27" s="1">
         <v>1.4055177624831652</v>
@@ -3794,16 +3788,16 @@
         <v>275</v>
       </c>
       <c r="D28" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E28" s="1">
-        <v>0.66155619908030971</v>
+        <v>0.66174017867960488</v>
       </c>
       <c r="F28" s="1">
-        <v>0.98253098593768773</v>
+        <v>0.98264763887038387</v>
       </c>
       <c r="G28" s="1">
-        <v>0.94559737590835125</v>
+        <v>0.94570528199978132</v>
       </c>
       <c r="H28" s="1">
         <v>0.19014615384615383</v>
@@ -3859,31 +3853,31 @@
         <v>276</v>
       </c>
       <c r="D29" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E29" s="1">
-        <v>0.77485644866200509</v>
+        <v>0.77504205257693726</v>
       </c>
       <c r="F29" s="1">
-        <v>0.60533652989130637</v>
+        <v>0.6053094695286001</v>
       </c>
       <c r="G29" s="1">
-        <v>0.77657429852279092</v>
+        <v>0.77653600174193993</v>
       </c>
       <c r="H29" s="1">
         <v>0.047848809523809509</v>
       </c>
       <c r="I29" s="1">
-        <v>-0.78778469285714281</v>
+        <v>-0.7877846928571427</v>
       </c>
       <c r="J29" s="1">
-        <v>0.19727728251020607</v>
+        <v>0.19727728251020604</v>
       </c>
       <c r="K29" s="1">
         <v>0.15602037024971496</v>
       </c>
       <c r="L29" s="1">
-        <v>0.16142557603773239</v>
+        <v>0.16142557603773236</v>
       </c>
       <c r="M29" s="1">
         <v>32</v>
@@ -3924,16 +3918,16 @@
         <v>277</v>
       </c>
       <c r="D30" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E30" s="1">
-        <v>0.82357430437933998</v>
+        <v>0.82383374068759641</v>
       </c>
       <c r="F30" s="1">
-        <v>0.82948122701011151</v>
+        <v>0.8296853052913743</v>
       </c>
       <c r="G30" s="1">
-        <v>0.76887312111997907</v>
+        <v>0.76905874082665859</v>
       </c>
       <c r="H30" s="1">
         <v>0.079837500000000006</v>
@@ -3989,31 +3983,31 @@
         <v>277</v>
       </c>
       <c r="D31" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E31" s="1">
-        <v>0.69201495819262937</v>
+        <v>0.69219697827686688</v>
       </c>
       <c r="F31" s="1">
-        <v>0.80050020028544899</v>
+        <v>0.80051438747437764</v>
       </c>
       <c r="G31" s="1">
-        <v>0.75742358732793513</v>
+        <v>0.75743351760440947</v>
       </c>
       <c r="H31" s="1">
-        <v>0.032460106382978721</v>
+        <v>0.032460106382978714</v>
       </c>
       <c r="I31" s="1">
         <v>0.47622105766666672</v>
       </c>
       <c r="J31" s="1">
-        <v>0.44643768989550425</v>
+        <v>0.44643768989550414</v>
       </c>
       <c r="K31" s="1">
-        <v>0.18147742104591102</v>
+        <v>0.18147742104591097</v>
       </c>
       <c r="L31" s="1">
-        <v>0.62635220850864692</v>
+        <v>0.6263522085086467</v>
       </c>
       <c r="M31" s="1">
         <v>33</v>
@@ -4054,16 +4048,16 @@
         <v>278</v>
       </c>
       <c r="D32" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E32" s="1">
-        <v>0.53867741461364937</v>
+        <v>0.53881965582845115</v>
       </c>
       <c r="F32" s="1">
-        <v>0.83162170785972411</v>
+        <v>0.83167080586367126</v>
       </c>
       <c r="G32" s="1">
-        <v>0.74309645766388099</v>
+        <v>0.74313690170706892</v>
       </c>
       <c r="H32" s="1">
         <v>0.069900000000000018</v>
@@ -4119,31 +4113,31 @@
         <v>279</v>
       </c>
       <c r="D33" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E33" s="1">
-        <v>1.0059789974550495</v>
+        <v>1.0062615382757452</v>
       </c>
       <c r="F33" s="1">
-        <v>0.7484226277540913</v>
+        <v>0.74850931832327805</v>
       </c>
       <c r="G33" s="1">
-        <v>0.69825468702000637</v>
+        <v>0.69833234570399372</v>
       </c>
       <c r="H33" s="1">
-        <v>0.23436226415094338</v>
+        <v>0.23436226415094336</v>
       </c>
       <c r="I33" s="1">
-        <v>1.0639914722222219</v>
+        <v>1.0639914722222221</v>
       </c>
       <c r="J33" s="1">
-        <v>0.52192637187223567</v>
+        <v>0.52192637187223578</v>
       </c>
       <c r="K33" s="1">
-        <v>3.9372398397351476</v>
+        <v>3.9372398397351467</v>
       </c>
       <c r="L33" s="1">
-        <v>2.2003842522066366</v>
+        <v>2.200384252206637</v>
       </c>
       <c r="M33" s="1">
         <v>27</v>
@@ -4184,31 +4178,31 @@
         <v>279</v>
       </c>
       <c r="D34" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E34" s="1">
-        <v>0.51586443508954039</v>
+        <v>0.51601563681843021</v>
       </c>
       <c r="F34" s="1">
-        <v>0.71798824227255298</v>
+        <v>0.71816681506801416</v>
       </c>
       <c r="G34" s="1">
-        <v>0.69710455649909719</v>
+        <v>0.69727471925409035</v>
       </c>
       <c r="H34" s="1">
-        <v>0.15674250000000003</v>
+        <v>0.15674250000000001</v>
       </c>
       <c r="I34" s="1">
         <v>1.0732575100000001</v>
       </c>
       <c r="J34" s="1">
-        <v>0.5274581701538007</v>
+        <v>0.52745817015380081</v>
       </c>
       <c r="K34" s="1">
-        <v>0.62748727321175946</v>
+        <v>0.62748727321175934</v>
       </c>
       <c r="L34" s="1">
-        <v>0.52989677580098837</v>
+        <v>0.52989677580098848</v>
       </c>
       <c r="M34" s="1">
         <v>42</v>
@@ -4249,16 +4243,16 @@
         <v>280</v>
       </c>
       <c r="D35" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E35" s="1">
-        <v>0.4211289929444525</v>
+        <v>0.42123910229720862</v>
       </c>
       <c r="F35" s="1">
-        <v>0.6497293745311522</v>
+        <v>0.64975654222892676</v>
       </c>
       <c r="G35" s="1">
-        <v>0.62941034094397452</v>
+        <v>0.62943375592103179</v>
       </c>
       <c r="H35" s="1">
         <v>0.0043999999999999994</v>
@@ -4314,16 +4308,16 @@
         <v>281</v>
       </c>
       <c r="D36" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E36" s="1">
-        <v>0.58931488691765144</v>
+        <v>0.58949660709025908</v>
       </c>
       <c r="F36" s="1">
-        <v>0.70100666192010141</v>
+        <v>0.70116208823372039</v>
       </c>
       <c r="G36" s="1">
-        <v>0.62918751005279017</v>
+        <v>0.6293241101169369</v>
       </c>
       <c r="H36" s="1">
         <v>0</v>
@@ -4350,7 +4344,7 @@
         <v>35</v>
       </c>
       <c r="P36" s="1">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Q36" s="1">
         <v>96</v>
@@ -4359,7 +4353,7 @@
         <v>113</v>
       </c>
       <c r="S36" s="1">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T36" s="1">
         <v>121</v>
@@ -4379,31 +4373,31 @@
         <v>282</v>
       </c>
       <c r="D37" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E37" s="1">
-        <v>0.33731354206825714</v>
+        <v>0.33740527869710391</v>
       </c>
       <c r="F37" s="1">
-        <v>0.5866549279913621</v>
+        <v>0.58671458618331829</v>
       </c>
       <c r="G37" s="1">
-        <v>0.53760309446061738</v>
+        <v>0.5376552846684558</v>
       </c>
       <c r="H37" s="1">
-        <v>0.11895454545454545</v>
+        <v>0.11895454545454544</v>
       </c>
       <c r="I37" s="1">
-        <v>0.92706852500000003</v>
+        <v>0.92706852499999992</v>
       </c>
       <c r="J37" s="1">
-        <v>0.47948830437955708</v>
+        <v>0.47948830437955692</v>
       </c>
       <c r="K37" s="1">
-        <v>0.36601980047606014</v>
+        <v>0.36601980047606009</v>
       </c>
       <c r="L37" s="1">
-        <v>0.37024283034590738</v>
+        <v>0.37024283034590727</v>
       </c>
       <c r="M37" s="1">
         <v>51</v>
@@ -4444,16 +4438,16 @@
         <v>283</v>
       </c>
       <c r="D38" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E38" s="1">
-        <v>0.53548371075765144</v>
+        <v>0.53565313523306723</v>
       </c>
       <c r="F38" s="1">
-        <v>0.53612960130304033</v>
+        <v>0.53626472073443632</v>
       </c>
       <c r="G38" s="1">
-        <v>0.49138023198923808</v>
+        <v>0.49150180641933849</v>
       </c>
       <c r="H38" s="1">
         <v>0.11125000000000002</v>
@@ -4509,16 +4503,16 @@
         <v>284</v>
       </c>
       <c r="D39" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E39" s="1">
-        <v>0.91971571178183531</v>
+        <v>0.91997641388967133</v>
       </c>
       <c r="F39" s="1">
-        <v>0.49924226335364724</v>
+        <v>0.49930648943335443</v>
       </c>
       <c r="G39" s="1">
-        <v>0.48678023651628594</v>
+        <v>0.48684061396343054</v>
       </c>
       <c r="H39" s="1">
         <v>0.14232888888888889</v>
@@ -4527,13 +4521,13 @@
         <v>0.54342682638888895</v>
       </c>
       <c r="J39" s="1">
-        <v>0.28410056631787317</v>
+        <v>0.28410056631787323</v>
       </c>
       <c r="K39" s="1">
         <v>4.0358010659017802</v>
       </c>
       <c r="L39" s="1">
-        <v>2.0215937764443792</v>
+        <v>2.0215937764443797</v>
       </c>
       <c r="M39" s="1">
         <v>28</v>
@@ -4574,16 +4568,16 @@
         <v>285</v>
       </c>
       <c r="D40" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E40" s="1">
-        <v>0.35799944201316097</v>
+        <v>0.35809859266237409</v>
       </c>
       <c r="F40" s="1">
-        <v>0.51240486703532706</v>
+        <v>0.51245696537087559</v>
       </c>
       <c r="G40" s="1">
-        <v>0.48259295028637322</v>
+        <v>0.48263979146679853</v>
       </c>
       <c r="H40" s="1">
         <v>0.12776000000000001</v>
@@ -4639,22 +4633,22 @@
         <v>286</v>
       </c>
       <c r="D41" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E41" s="1">
-        <v>0.69200434455323501</v>
+        <v>0.69218085638500493</v>
       </c>
       <c r="F41" s="1">
-        <v>0.43790487429894659</v>
+        <v>0.43791115318899076</v>
       </c>
       <c r="G41" s="1">
-        <v>0.46113373657562473</v>
+        <v>0.46113822164929857</v>
       </c>
       <c r="H41" s="1">
         <v>0.30681785714285709</v>
       </c>
       <c r="I41" s="1">
-        <v>1.0370763017241378</v>
+        <v>1.037076301724138</v>
       </c>
       <c r="J41" s="1">
         <v>0.55183306601524518</v>
@@ -4704,31 +4698,31 @@
         <v>286</v>
       </c>
       <c r="D42" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E42" s="1">
-        <v>0.62860270407949181</v>
+        <v>0.62875123798744537</v>
       </c>
       <c r="F42" s="1">
-        <v>0.44747770326531466</v>
+        <v>0.44746541979947568</v>
       </c>
       <c r="G42" s="1">
-        <v>0.43779880963652296</v>
+        <v>0.43778477268961991</v>
       </c>
       <c r="H42" s="1">
-        <v>0.053105446808510641</v>
+        <v>0.053105446808510634</v>
       </c>
       <c r="I42" s="1">
         <v>0.32435879676595736</v>
       </c>
       <c r="J42" s="1">
-        <v>0.43319793711247406</v>
+        <v>0.43319793711247401</v>
       </c>
       <c r="K42" s="1">
         <v>1.2946672962968004</v>
       </c>
       <c r="L42" s="1">
-        <v>2.6502728719378736</v>
+        <v>2.6502728719378732</v>
       </c>
       <c r="M42" s="1">
         <v>36</v>
@@ -4769,31 +4763,31 @@
         <v>287</v>
       </c>
       <c r="D43" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E43" s="1">
-        <v>0.36638853415834011</v>
+        <v>0.3664954629984758</v>
       </c>
       <c r="F43" s="1">
-        <v>0.41376339404998108</v>
+        <v>0.41380668523577713</v>
       </c>
       <c r="G43" s="1">
-        <v>0.39764350245230584</v>
+        <v>0.39768327283495625</v>
       </c>
       <c r="H43" s="1">
-        <v>0.010643103448275865</v>
+        <v>0.010643103448275864</v>
       </c>
       <c r="I43" s="1">
         <v>0.30221221083333333</v>
       </c>
       <c r="J43" s="1">
-        <v>0.3976290711911421</v>
+        <v>0.39762907119114205</v>
       </c>
       <c r="K43" s="1">
-        <v>0.019603460012927638</v>
+        <v>0.019603460012927634</v>
       </c>
       <c r="L43" s="1">
-        <v>0.18379245431422656</v>
+        <v>0.18379245431422653</v>
       </c>
       <c r="M43" s="1">
         <v>48</v>
@@ -4834,16 +4828,16 @@
         <v>288</v>
       </c>
       <c r="D44" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E44" s="1">
-        <v>0.24256160419281816</v>
+        <v>0.24262510619262576</v>
       </c>
       <c r="F44" s="1">
-        <v>0.4062615675502288</v>
+        <v>0.40629047414641589</v>
       </c>
       <c r="G44" s="1">
-        <v>0.39731521525753732</v>
+        <v>0.39734165265938903</v>
       </c>
       <c r="H44" s="1">
         <v>0.15309999999999999</v>
@@ -4899,16 +4893,16 @@
         <v>288</v>
       </c>
       <c r="D45" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E45" s="1">
-        <v>0.21742707852310017</v>
+        <v>0.21748171933271554</v>
       </c>
       <c r="F45" s="1">
-        <v>0.39684475525543089</v>
+        <v>0.39684530234126436</v>
       </c>
       <c r="G45" s="1">
-        <v>0.37657795368425295</v>
+        <v>0.37657673596593805</v>
       </c>
       <c r="H45" s="1">
         <v>0.26424999999999998</v>
@@ -4964,31 +4958,31 @@
         <v>289</v>
       </c>
       <c r="D46" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E46" s="1">
-        <v>0.35754386057291132</v>
+        <v>0.35763770848155652</v>
       </c>
       <c r="F46" s="1">
-        <v>0.39729520329458134</v>
+        <v>0.39726327215406693</v>
       </c>
       <c r="G46" s="1">
-        <v>0.37548557481737521</v>
+        <v>0.37545366486084547</v>
       </c>
       <c r="H46" s="1">
-        <v>0.046331294964028776</v>
+        <v>0.046331294964028789</v>
       </c>
       <c r="I46" s="1">
-        <v>0.59265171857142851</v>
+        <v>0.59265171857142862</v>
       </c>
       <c r="J46" s="1">
-        <v>0.46670171370148167</v>
+        <v>0.46670171370148172</v>
       </c>
       <c r="K46" s="1">
-        <v>0.56129717636821741</v>
+        <v>0.56129717636821763</v>
       </c>
       <c r="L46" s="1">
-        <v>1.4188710083707523</v>
+        <v>1.4188710083707525</v>
       </c>
       <c r="M46" s="1">
         <v>50</v>
@@ -5029,16 +5023,16 @@
         <v>290</v>
       </c>
       <c r="D47" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E47" s="1">
-        <v>0.44923516602035052</v>
+        <v>0.44934683417535259</v>
       </c>
       <c r="F47" s="1">
-        <v>0.38353664931308756</v>
+        <v>0.38351538871967478</v>
       </c>
       <c r="G47" s="1">
-        <v>0.36925191643785826</v>
+        <v>0.36922974471185227</v>
       </c>
       <c r="H47" s="1">
         <v>0.30947142857142856</v>
@@ -5094,31 +5088,31 @@
         <v>291</v>
       </c>
       <c r="D48" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E48" s="1">
-        <v>0.56677085224253698</v>
+        <v>0.56691402549024905</v>
       </c>
       <c r="F48" s="1">
-        <v>0.36677254946681159</v>
+        <v>0.36678040658546684</v>
       </c>
       <c r="G48" s="1">
-        <v>0.35986589590457707</v>
+        <v>0.35987194524874178</v>
       </c>
       <c r="H48" s="1">
-        <v>0.016655714285714281</v>
+        <v>0.016655714285714284</v>
       </c>
       <c r="I48" s="1">
-        <v>0.22443145297682707</v>
+        <v>0.22443145297682709</v>
       </c>
       <c r="J48" s="1">
-        <v>0.2897102942003314</v>
+        <v>0.28971029420033151</v>
       </c>
       <c r="K48" s="1">
-        <v>0.17551606749633206</v>
+        <v>0.17551606749633208</v>
       </c>
       <c r="L48" s="1">
-        <v>0.76613031177892599</v>
+        <v>0.76613031177892632</v>
       </c>
       <c r="M48" s="1">
         <v>38</v>
@@ -5159,16 +5153,16 @@
         <v>292</v>
       </c>
       <c r="D49" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E49" s="1">
-        <v>1.0744018364075281</v>
+        <v>1.0746976094944141</v>
       </c>
       <c r="F49" s="1">
-        <v>0.37208875236918754</v>
+        <v>0.37212421109175997</v>
       </c>
       <c r="G49" s="1">
-        <v>0.35361773681719455</v>
+        <v>0.35364980419837494</v>
       </c>
       <c r="H49" s="1">
         <v>0.20480000000000001</v>
@@ -5224,31 +5218,31 @@
         <v>293</v>
       </c>
       <c r="D50" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E50" s="1">
-        <v>0.24954105237019311</v>
+        <v>0.24961382439676705</v>
       </c>
       <c r="F50" s="1">
-        <v>0.37368681129396469</v>
+        <v>0.37373406730751385</v>
       </c>
       <c r="G50" s="1">
-        <v>0.35231981767931392</v>
+        <v>0.35236274646321986</v>
       </c>
       <c r="H50" s="1">
-        <v>0.02781764705882353</v>
+        <v>0.027817647058823534</v>
       </c>
       <c r="I50" s="1">
-        <v>0.97841360833333313</v>
+        <v>0.97841360833333335</v>
       </c>
       <c r="J50" s="1">
-        <v>0.42829839638714728</v>
+        <v>0.42829839638714734</v>
       </c>
       <c r="K50" s="1">
-        <v>0.013217807046634361</v>
+        <v>0.013217807046634365</v>
       </c>
       <c r="L50" s="1">
-        <v>0.051070553439700676</v>
+        <v>0.051070553439700683</v>
       </c>
       <c r="M50" s="1">
         <v>58</v>
@@ -5289,16 +5283,16 @@
         <v>294</v>
       </c>
       <c r="D51" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E51" s="1">
-        <v>0.21725246138409915</v>
+        <v>0.21731393518671405</v>
       </c>
       <c r="F51" s="1">
-        <v>0.32452624845874245</v>
+        <v>0.32456458428506907</v>
       </c>
       <c r="G51" s="1">
-        <v>0.30510742749865749</v>
+        <v>0.30514206201688771</v>
       </c>
       <c r="H51" s="1">
         <v>0.054039999999999998</v>
@@ -5354,25 +5348,25 @@
         <v>295</v>
       </c>
       <c r="D52" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E52" s="1">
-        <v>0.26988646043411491</v>
+        <v>0.26995598298738954</v>
       </c>
       <c r="F52" s="1">
-        <v>0.32901863523167746</v>
+        <v>0.3290075793937165</v>
       </c>
       <c r="G52" s="1">
-        <v>0.30026820067789706</v>
+        <v>0.30025672606758108</v>
       </c>
       <c r="H52" s="1">
         <v>0.088489999999999999</v>
       </c>
       <c r="I52" s="1">
-        <v>0.94483917500000014</v>
+        <v>0.94483917500000003</v>
       </c>
       <c r="J52" s="1">
-        <v>0.49194354237827326</v>
+        <v>0.4919435423782732</v>
       </c>
       <c r="K52" s="1">
         <v>0.018086878811458668</v>
@@ -5419,16 +5413,16 @@
         <v>295</v>
       </c>
       <c r="D53" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E53" s="1">
-        <v>0.2605530771466158</v>
+        <v>0.26062548646717998</v>
       </c>
       <c r="F53" s="1">
-        <v>0.31147557084227617</v>
+        <v>0.31149562907837708</v>
       </c>
       <c r="G53" s="1">
-        <v>0.28442014202900034</v>
+        <v>0.28443714607006471</v>
       </c>
       <c r="H53" s="1">
         <v>0.086641666666666672</v>
@@ -5484,16 +5478,16 @@
         <v>296</v>
       </c>
       <c r="D54" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E54" s="1">
-        <v>0.44919162221743641</v>
+        <v>0.44931041975676944</v>
       </c>
       <c r="F54" s="1">
-        <v>0.27462508450240114</v>
+        <v>0.27463584871417956</v>
       </c>
       <c r="G54" s="1">
-        <v>0.27645197094336055</v>
+        <v>0.27646153165322279</v>
       </c>
       <c r="H54" s="1">
         <v>0.35620000000000002</v>
@@ -5549,16 +5543,16 @@
         <v>297</v>
       </c>
       <c r="D55" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E55" s="1">
-        <v>0.26734045316381422</v>
+        <v>0.26741150879924169</v>
       </c>
       <c r="F55" s="1">
-        <v>0.27301605850413674</v>
+        <v>0.27301305543567395</v>
       </c>
       <c r="G55" s="1">
-        <v>0.25610942466688935</v>
+        <v>0.25610542634346212</v>
       </c>
       <c r="H55" s="1">
         <v>0.018618750000000003</v>
@@ -5614,16 +5608,16 @@
         <v>298</v>
       </c>
       <c r="D56" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E56" s="1">
-        <v>0.18816215079047185</v>
+        <v>0.18820332732596867</v>
       </c>
       <c r="F56" s="1">
-        <v>0.25290580081209302</v>
+        <v>0.25286698536783675</v>
       </c>
       <c r="G56" s="1">
-        <v>0.25218733178269231</v>
+        <v>0.25214746364139445</v>
       </c>
       <c r="H56" s="1">
         <v>0.017951851851851854</v>
@@ -5679,16 +5673,16 @@
         <v>299</v>
       </c>
       <c r="D57" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E57" s="1">
-        <v>0.82944159847165944</v>
+        <v>0.82971382920928782</v>
       </c>
       <c r="F57" s="1">
-        <v>0.25512304105006994</v>
+        <v>0.25517664857464528</v>
       </c>
       <c r="G57" s="1">
-        <v>0.23849197171397718</v>
+        <v>0.23854098443872457</v>
       </c>
       <c r="H57" s="1">
         <v>0.10803750000000001</v>
@@ -5744,16 +5738,16 @@
         <v>300</v>
       </c>
       <c r="D58" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E58" s="1">
-        <v>0.44145852848889888</v>
+        <v>0.44154458757937098</v>
       </c>
       <c r="F58" s="1">
-        <v>0.22932817896895458</v>
+        <v>0.22928377148301732</v>
       </c>
       <c r="G58" s="1">
-        <v>0.22816798567459234</v>
+        <v>0.22812275069214108</v>
       </c>
       <c r="H58" s="1">
         <v>0.215475</v>
@@ -5809,16 +5803,16 @@
         <v>301</v>
       </c>
       <c r="D59" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E59" s="1">
-        <v>0.54382773680945984</v>
+        <v>0.54397262979766192</v>
       </c>
       <c r="F59" s="1">
-        <v>0.24178403328518971</v>
+        <v>0.24179888519389728</v>
       </c>
       <c r="G59" s="1">
-        <v>0.22720139842909004</v>
+        <v>0.22721430661159736</v>
       </c>
       <c r="H59" s="1">
         <v>0.15590000000000001</v>
@@ -5874,16 +5868,16 @@
         <v>301</v>
       </c>
       <c r="D60" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E60" s="1">
-        <v>0.15111842442330253</v>
+        <v>0.1511595840837428</v>
       </c>
       <c r="F60" s="1">
-        <v>0.23087971384529354</v>
+        <v>0.23089554329085837</v>
       </c>
       <c r="G60" s="1">
-        <v>0.21310811453131781</v>
+        <v>0.21312174256053665</v>
       </c>
       <c r="H60" s="1">
         <v>0.085550000000000001</v>
@@ -5939,31 +5933,31 @@
         <v>302</v>
       </c>
       <c r="D61" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E61" s="1">
-        <v>0.19084597339702836</v>
+        <v>0.1909049876855442</v>
       </c>
       <c r="F61" s="1">
-        <v>0.18265519677660044</v>
+        <v>0.1826842905681148</v>
       </c>
       <c r="G61" s="1">
-        <v>0.20383640698723215</v>
+        <v>0.20386793428754502</v>
       </c>
       <c r="H61" s="1">
-        <v>0.10163928571428572</v>
+        <v>0.10163928571428571</v>
       </c>
       <c r="I61" s="1">
-        <v>-0.33637217857142865</v>
+        <v>-0.33637217857142859</v>
       </c>
       <c r="J61" s="1">
-        <v>0.39330048746661395</v>
+        <v>0.39330048746661389</v>
       </c>
       <c r="K61" s="1">
         <v>0.38381469686377151</v>
       </c>
       <c r="L61" s="1">
-        <v>0.37270874396293519</v>
+        <v>0.37270874396293507</v>
       </c>
       <c r="M61" s="1">
         <v>65</v>
@@ -6004,31 +5998,31 @@
         <v>302</v>
       </c>
       <c r="D62" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E62" s="1">
-        <v>0.14343670198881661</v>
+        <v>0.14347556585537086</v>
       </c>
       <c r="F62" s="1">
-        <v>0.19130097472229379</v>
+        <v>0.19131648553625255</v>
       </c>
       <c r="G62" s="1">
-        <v>0.19218359823251277</v>
+        <v>0.19219829414436954</v>
       </c>
       <c r="H62" s="1">
-        <v>0.19395714285714291</v>
+        <v>0.19395714285714288</v>
       </c>
       <c r="I62" s="1">
         <v>1.0456717066666668</v>
       </c>
       <c r="J62" s="1">
-        <v>0.32520460672634594</v>
+        <v>0.32520460672634588</v>
       </c>
       <c r="K62" s="1">
-        <v>3.8130055548305259</v>
+        <v>3.8130055548305251</v>
       </c>
       <c r="L62" s="1">
-        <v>1.6043660000000417</v>
+        <v>1.6043660000000415</v>
       </c>
       <c r="M62" s="1">
         <v>74</v>
@@ -6069,16 +6063,16 @@
         <v>303</v>
       </c>
       <c r="D63" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E63" s="1">
-        <v>0.28885820847317462</v>
+        <v>0.28893830535038095</v>
       </c>
       <c r="F63" s="1">
-        <v>0.20506647300029987</v>
+        <v>0.20507907112625628</v>
       </c>
       <c r="G63" s="1">
-        <v>0.18998207603920508</v>
+        <v>0.18999287117113672</v>
       </c>
       <c r="H63" s="1">
         <v>0.046700000000000005</v>
@@ -6134,16 +6128,16 @@
         <v>304</v>
       </c>
       <c r="D64" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E64" s="1">
-        <v>0.10832447930983284</v>
+        <v>0.10836138961870946</v>
       </c>
       <c r="F64" s="1">
-        <v>0.12790307038131479</v>
+        <v>0.12794807916949161</v>
       </c>
       <c r="G64" s="1">
-        <v>0.18203972927774453</v>
+        <v>0.18210294872463523</v>
       </c>
       <c r="H64" s="1">
         <v>0.01968421052631579</v>
@@ -6199,16 +6193,16 @@
         <v>305</v>
       </c>
       <c r="D65" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E65" s="1">
-        <v>0.086739827576613762</v>
+        <v>0.086754790983553848</v>
       </c>
       <c r="F65" s="1">
-        <v>0.11400633613657835</v>
+        <v>0.11397773868395805</v>
       </c>
       <c r="G65" s="1">
-        <v>0.17299715154810785</v>
+        <v>0.17295295908431757</v>
       </c>
       <c r="H65" s="1">
         <v>0.024319999999999994</v>
@@ -6264,16 +6258,16 @@
         <v>306</v>
       </c>
       <c r="D66" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E66" s="1">
-        <v>0.17050752758955495</v>
+        <v>0.17055110024146994</v>
       </c>
       <c r="F66" s="1">
-        <v>0.16316072978232982</v>
+        <v>0.16315658445656728</v>
       </c>
       <c r="G66" s="1">
-        <v>0.15365917453773567</v>
+        <v>0.15365456191958377</v>
       </c>
       <c r="H66" s="1">
         <v>0.0064250000000000002</v>
@@ -6329,16 +6323,16 @@
         <v>307</v>
       </c>
       <c r="D67" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E67" s="1">
-        <v>0.098650562461290697</v>
+        <v>0.098682961059604363</v>
       </c>
       <c r="F67" s="1">
-        <v>0.16521288706196166</v>
+        <v>0.16525791864575723</v>
       </c>
       <c r="G67" s="1">
-        <v>0.15152903574689425</v>
+        <v>0.15156963848769156</v>
       </c>
       <c r="H67" s="1">
         <v>0.032329999999999991</v>
@@ -6394,16 +6388,16 @@
         <v>308</v>
       </c>
       <c r="D68" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E68" s="1">
-        <v>0.2040953173433423</v>
+        <v>0.2041594412737319</v>
       </c>
       <c r="F68" s="1">
-        <v>0.1519172343330136</v>
+        <v>0.15193929476161622</v>
       </c>
       <c r="G68" s="1">
-        <v>0.13408056839643345</v>
+        <v>0.1340994202013803</v>
       </c>
       <c r="H68" s="1">
         <v>0.036928571428571422</v>
@@ -6459,31 +6453,31 @@
         <v>309</v>
       </c>
       <c r="D69" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E69" s="1">
-        <v>0.29795487315695246</v>
+        <v>0.2980312723277691</v>
       </c>
       <c r="F69" s="1">
-        <v>0.13572272958805165</v>
+        <v>0.13573104461110569</v>
       </c>
       <c r="G69" s="1">
-        <v>0.12983269281073467</v>
+        <v>0.12984004812773906</v>
       </c>
       <c r="H69" s="1">
-        <v>0.090175813382443196</v>
+        <v>0.09017581338244321</v>
       </c>
       <c r="I69" s="1">
-        <v>0.034687566626984107</v>
+        <v>0.034687566626984113</v>
       </c>
       <c r="J69" s="1">
-        <v>0.34878663544164012</v>
+        <v>0.34878663544164018</v>
       </c>
       <c r="K69" s="1">
-        <v>1.1760083096439029</v>
+        <v>1.1760083096439031</v>
       </c>
       <c r="L69" s="1">
-        <v>1.1414719886248399</v>
+        <v>1.1414719886248401</v>
       </c>
       <c r="M69" s="1">
         <v>53</v>
@@ -6524,19 +6518,19 @@
         <v>310</v>
       </c>
       <c r="D70" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E70" s="1">
-        <v>0.15833236049065091</v>
+        <v>0.15837751734983502</v>
       </c>
       <c r="F70" s="1">
-        <v>0.12103241958268983</v>
+        <v>0.12107026667922324</v>
       </c>
       <c r="G70" s="1">
-        <v>0.11904915045258335</v>
+        <v>0.11908582812347818</v>
       </c>
       <c r="H70" s="1">
-        <v>0.042937154150197623</v>
+        <v>0.04293715415019763</v>
       </c>
       <c r="I70" s="1">
         <v>0.12196690362537764</v>
@@ -6545,7 +6539,7 @@
         <v>0.27821509227660179</v>
       </c>
       <c r="K70" s="1">
-        <v>0.41756737499897667</v>
+        <v>0.41756737499897678</v>
       </c>
       <c r="L70" s="1">
         <v>0.67898329471164454</v>
@@ -6589,31 +6583,31 @@
         <v>311</v>
       </c>
       <c r="D71" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E71" s="1">
-        <v>0.13465382171144069</v>
+        <v>0.13469350286335716</v>
       </c>
       <c r="F71" s="1">
-        <v>0.12245709434778677</v>
+        <v>0.12247954830884522</v>
       </c>
       <c r="G71" s="1">
-        <v>0.1161678381195529</v>
+        <v>0.11618860298044371</v>
       </c>
       <c r="H71" s="1">
         <v>0.02184070929070929</v>
       </c>
       <c r="I71" s="1">
-        <v>-0.69464828129370637</v>
+        <v>-0.69464828129370626</v>
       </c>
       <c r="J71" s="1">
-        <v>0.22603563202011162</v>
+        <v>0.22603563202011159</v>
       </c>
       <c r="K71" s="1">
         <v>0.1096364783096502</v>
       </c>
       <c r="L71" s="1">
-        <v>0.28474122276042513</v>
+        <v>0.28474122276042507</v>
       </c>
       <c r="M71" s="1">
         <v>75</v>
@@ -6654,16 +6648,16 @@
         <v>312</v>
       </c>
       <c r="D72" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E72" s="1">
-        <v>0.085134933587850264</v>
+        <v>0.085154634523792114</v>
       </c>
       <c r="F72" s="1">
-        <v>0.1255662340185931</v>
+        <v>0.12555507567206567</v>
       </c>
       <c r="G72" s="1">
-        <v>0.11454845438382001</v>
+        <v>0.11453774684751215</v>
       </c>
       <c r="H72" s="1">
         <v>0.15089999999999995</v>
@@ -6719,16 +6713,16 @@
         <v>313</v>
       </c>
       <c r="D73" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E73" s="1">
-        <v>0.22348332786924649</v>
+        <v>0.22355830833536433</v>
       </c>
       <c r="F73" s="1">
-        <v>0.11049098356226161</v>
+        <v>0.11052895326868384</v>
       </c>
       <c r="G73" s="1">
-        <v>0.10807178032379773</v>
+        <v>0.1081084200597823</v>
       </c>
       <c r="H73" s="1">
         <v>0.26696666666666674</v>
@@ -6784,16 +6778,16 @@
         <v>314</v>
       </c>
       <c r="D74" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E74" s="1">
-        <v>0.18808312344209949</v>
+        <v>0.18812974978279184</v>
       </c>
       <c r="F74" s="1">
-        <v>0.1020556076688383</v>
+        <v>0.10205258013850733</v>
       </c>
       <c r="G74" s="1">
-        <v>0.1030294646686056</v>
+        <v>0.10302593306737123</v>
       </c>
       <c r="H74" s="1">
         <v>0.1323</v>
@@ -6849,16 +6843,16 @@
         <v>314</v>
       </c>
       <c r="D75" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E75" s="1">
-        <v>0.12408252519117574</v>
+        <v>0.12410765355938266</v>
       </c>
       <c r="F75" s="1">
-        <v>0.089596863510123914</v>
+        <v>0.08957758325971038</v>
       </c>
       <c r="G75" s="1">
-        <v>0.094726930593763303</v>
+        <v>0.094706109601983585</v>
       </c>
       <c r="H75" s="1">
         <v>0.021781034482758616</v>
@@ -6914,22 +6908,22 @@
         <v>314</v>
       </c>
       <c r="D76" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E76" s="1">
-        <v>0.14723677729030979</v>
+        <v>0.14727658286536899</v>
       </c>
       <c r="F76" s="1">
-        <v>0.093749597377174518</v>
+        <v>0.093758803435642954</v>
       </c>
       <c r="G76" s="1">
-        <v>0.094596265904748206</v>
+        <v>0.09460511876260938</v>
       </c>
       <c r="H76" s="1">
         <v>0.047746875000000008</v>
       </c>
       <c r="I76" s="1">
-        <v>1.0681294804347823</v>
+        <v>1.0681294804347825</v>
       </c>
       <c r="J76" s="1">
         <v>0.35252476706336816</v>
@@ -6979,16 +6973,16 @@
         <v>315</v>
       </c>
       <c r="D77" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E77" s="1">
-        <v>0.33539430749445132</v>
+        <v>0.33549071040923062</v>
       </c>
       <c r="F77" s="1">
-        <v>0.057527129512984887</v>
+        <v>0.057529539858307416</v>
       </c>
       <c r="G77" s="1">
-        <v>0.091536593730414686</v>
+        <v>0.091540006842776578</v>
       </c>
       <c r="H77" s="1">
         <v>0.0086196178343949052</v>
@@ -7044,16 +7038,16 @@
         <v>316</v>
       </c>
       <c r="D78" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E78" s="1">
-        <v>0.16782104346259874</v>
+        <v>0.16786119104536784</v>
       </c>
       <c r="F78" s="1">
-        <v>0.08940817726425343</v>
+        <v>0.089406609409248966</v>
       </c>
       <c r="G78" s="1">
-        <v>0.08626662704066855</v>
+        <v>0.086264716401553879</v>
       </c>
       <c r="H78" s="1">
         <v>0.0034639455782312922</v>
@@ -7109,28 +7103,28 @@
         <v>317</v>
       </c>
       <c r="D79" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E79" s="1">
-        <v>0.12913214287645364</v>
+        <v>0.12916646808594057</v>
       </c>
       <c r="F79" s="1">
-        <v>0.08384309068544836</v>
+        <v>0.083858841160859912</v>
       </c>
       <c r="G79" s="1">
-        <v>0.084691702300438404</v>
+        <v>0.084707221502570373</v>
       </c>
       <c r="H79" s="1">
-        <v>0.02323065134099617</v>
+        <v>0.023230651340996174</v>
       </c>
       <c r="I79" s="1">
-        <v>0.22154538309692665</v>
+        <v>0.22154538309692684</v>
       </c>
       <c r="J79" s="1">
-        <v>0.20306663040463757</v>
+        <v>0.2030666304046376</v>
       </c>
       <c r="K79" s="1">
-        <v>0.018732116380411716</v>
+        <v>0.01873211638041172</v>
       </c>
       <c r="L79" s="1">
         <v>0.041091228336643304</v>
@@ -7174,16 +7168,16 @@
         <v>318</v>
       </c>
       <c r="D80" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E80" s="1">
-        <v>0.0777443466354414</v>
+        <v>0.077761687844086047</v>
       </c>
       <c r="F80" s="1">
-        <v>0.082079971423879294</v>
+        <v>0.082066559060039457</v>
       </c>
       <c r="G80" s="1">
-        <v>0.083758765699955801</v>
+        <v>0.083744692759848846</v>
       </c>
       <c r="H80" s="1">
         <v>0.057899999999999993</v>
@@ -7239,16 +7233,16 @@
         <v>319</v>
       </c>
       <c r="D81" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E81" s="1">
-        <v>0.043803905850451096</v>
+        <v>0.043820498346318987</v>
       </c>
       <c r="F81" s="1">
-        <v>0.05043777605111243</v>
+        <v>0.050463235424104698</v>
       </c>
       <c r="G81" s="1">
-        <v>0.074941064228465304</v>
+        <v>0.074978546256580111</v>
       </c>
       <c r="H81" s="1">
         <v>0.0049828571428571439</v>
@@ -7304,19 +7298,19 @@
         <v>320</v>
       </c>
       <c r="D82" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E82" s="1">
-        <v>0.37951871878243082</v>
+        <v>0.37962799822053572</v>
       </c>
       <c r="F82" s="1">
-        <v>0.081821292354062533</v>
+        <v>0.08182808394183759</v>
       </c>
       <c r="G82" s="1">
-        <v>0.07222291088937409</v>
+        <v>0.0722285726262102</v>
       </c>
       <c r="H82" s="1">
-        <v>0.015222222222222222</v>
+        <v>0.015222222222222224</v>
       </c>
       <c r="I82" s="1">
         <v>-0.58393884166666676</v>
@@ -7369,16 +7363,16 @@
         <v>320</v>
       </c>
       <c r="D83" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E83" s="1">
-        <v>0.056123322575771802</v>
+        <v>0.056138773428646704</v>
       </c>
       <c r="F83" s="1">
-        <v>0.039825003843767928</v>
+        <v>0.039833305703890258</v>
       </c>
       <c r="G83" s="1">
-        <v>0.069426159032626125</v>
+        <v>0.069440311229029064</v>
       </c>
       <c r="H83" s="1">
         <v>0.045200000000000004</v>
@@ -7434,31 +7428,31 @@
         <v>321</v>
       </c>
       <c r="D84" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E84" s="1">
-        <v>0.1280196957944838</v>
+        <v>0.12804252418396198</v>
       </c>
       <c r="F84" s="1">
-        <v>0.068983508536142574</v>
+        <v>0.068964507562829</v>
       </c>
       <c r="G84" s="1">
-        <v>0.066108060236397814</v>
+        <v>0.066089546461806231</v>
       </c>
       <c r="H84" s="1">
         <v>0.010081632653061223</v>
       </c>
       <c r="I84" s="1">
-        <v>-1.1254234883333336</v>
+        <v>-1.1254234883333338</v>
       </c>
       <c r="J84" s="1">
-        <v>0.10396575835554332</v>
+        <v>0.10396575835554334</v>
       </c>
       <c r="K84" s="1">
         <v>0.1386445718871219</v>
       </c>
       <c r="L84" s="1">
-        <v>0.3587958645167611</v>
+        <v>0.35879586451676115</v>
       </c>
       <c r="M84" s="1">
         <v>78</v>
@@ -7499,16 +7493,16 @@
         <v>322</v>
       </c>
       <c r="D85" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E85" s="1">
-        <v>0.20590250782602601</v>
+        <v>0.20596091995880042</v>
       </c>
       <c r="F85" s="1">
-        <v>0.064482147205829968</v>
+        <v>0.064489318410531529</v>
       </c>
       <c r="G85" s="1">
-        <v>0.062208994824576438</v>
+        <v>0.062215626273110509</v>
       </c>
       <c r="H85" s="1">
         <v>0.17670000000000002</v>
@@ -7564,16 +7558,16 @@
         <v>322</v>
       </c>
       <c r="D86" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E86" s="1">
-        <v>0.047124228553552992</v>
+        <v>0.04713689303534957</v>
       </c>
       <c r="F86" s="1">
-        <v>0.049100750767439583</v>
+        <v>0.049103901509924788</v>
       </c>
       <c r="G86" s="1">
-        <v>0.047448223974409634</v>
+        <v>0.04745104982010747</v>
       </c>
       <c r="H86" s="1">
         <v>0.19901874999999999</v>
@@ -7629,16 +7623,16 @@
         <v>323</v>
       </c>
       <c r="D87" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E87" s="1">
-        <v>0.05373714216136135</v>
+        <v>0.053757214313370022</v>
       </c>
       <c r="F87" s="1">
-        <v>0.051677339071471678</v>
+        <v>0.051701671902905755</v>
       </c>
       <c r="G87" s="1">
-        <v>0.045789530722585757</v>
+        <v>0.04581087992502423</v>
       </c>
       <c r="H87" s="1">
         <v>0.00093478260869565204</v>
@@ -7694,16 +7688,16 @@
         <v>324</v>
       </c>
       <c r="D88" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E88" s="1">
-        <v>0.062714633847459206</v>
+        <v>0.062738845918717895</v>
       </c>
       <c r="F88" s="1">
-        <v>0.045468565921286272</v>
+        <v>0.045492155613525473</v>
       </c>
       <c r="G88" s="1">
-        <v>0.045531966505913998</v>
+        <v>0.045555378978597363</v>
       </c>
       <c r="H88" s="1">
         <v>0.0047085714285714292</v>
@@ -7759,16 +7753,16 @@
         <v>325</v>
       </c>
       <c r="D89" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E89" s="1">
-        <v>0.069481011358344266</v>
+        <v>0.069505940940096378</v>
       </c>
       <c r="F89" s="1">
-        <v>0.045931452541512589</v>
+        <v>0.045950493623770322</v>
       </c>
       <c r="G89" s="1">
-        <v>0.045217202263254062</v>
+        <v>0.045235738611614437</v>
       </c>
       <c r="H89" s="1">
         <v>0.014700000000000001</v>
@@ -7824,31 +7818,31 @@
         <v>325</v>
       </c>
       <c r="D90" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E90" s="1">
-        <v>0.056857201778984373</v>
+        <v>0.056869881413318259</v>
       </c>
       <c r="F90" s="1">
-        <v>0.043326799900765281</v>
+        <v>0.043326957330007312</v>
       </c>
       <c r="G90" s="1">
-        <v>0.03977489237216536</v>
+        <v>0.039774853444033489</v>
       </c>
       <c r="H90" s="1">
-        <v>0.013527564102564105</v>
+        <v>0.013527564102564107</v>
       </c>
       <c r="I90" s="1">
-        <v>-0.84993066923076954</v>
+        <v>-0.84993066923076965</v>
       </c>
       <c r="J90" s="1">
-        <v>0.17650879898658117</v>
+        <v>0.1765087989865812</v>
       </c>
       <c r="K90" s="1">
-        <v>0.13660299724075317</v>
+        <v>0.1366029972407532</v>
       </c>
       <c r="L90" s="1">
-        <v>0.44729298646185511</v>
+        <v>0.44729298646185517</v>
       </c>
       <c r="M90" s="1">
         <v>95</v>
@@ -7889,28 +7883,28 @@
         <v>325</v>
       </c>
       <c r="D91" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E91" s="1">
-        <v>0.068233819329387282</v>
+        <v>0.068239945984231359</v>
       </c>
       <c r="F91" s="1">
-        <v>0.041213793457482481</v>
+        <v>0.041202919560218404</v>
       </c>
       <c r="G91" s="1">
-        <v>0.037639776414988294</v>
+        <v>0.037629671933411289</v>
       </c>
       <c r="H91" s="1">
-        <v>0.018383974358974365</v>
+        <v>0.018383974358974361</v>
       </c>
       <c r="I91" s="1">
-        <v>-0.99740813119658123</v>
+        <v>-0.99740813119658134</v>
       </c>
       <c r="J91" s="1">
         <v>0.14914368878290427</v>
       </c>
       <c r="K91" s="1">
-        <v>0.1999059530899247</v>
+        <v>0.19990595308992465</v>
       </c>
       <c r="L91" s="1">
         <v>0.40698303192733865</v>
@@ -7954,16 +7948,16 @@
         <v>326</v>
       </c>
       <c r="D92" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E92" s="1">
-        <v>0.1530467369802998</v>
+        <v>0.15308388760578182</v>
       </c>
       <c r="F92" s="1">
-        <v>0.038843071821467769</v>
+        <v>0.038839918167703394</v>
       </c>
       <c r="G92" s="1">
-        <v>0.035313804273208182</v>
+        <v>0.035310774297312865</v>
       </c>
       <c r="H92" s="1">
         <v>0.015656132344552195</v>
@@ -7972,13 +7966,13 @@
         <v>0.41390604934210512</v>
       </c>
       <c r="J92" s="1">
-        <v>0.31892117114673452</v>
+        <v>0.31892117114673463</v>
       </c>
       <c r="K92" s="1">
         <v>0.083638259606170717</v>
       </c>
       <c r="L92" s="1">
-        <v>0.42755201185736802</v>
+        <v>0.42755201185736808</v>
       </c>
       <c r="M92" s="1">
         <v>71</v>
@@ -8019,16 +8013,16 @@
         <v>327</v>
       </c>
       <c r="D93" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E93" s="1">
-        <v>0.072018758941478037</v>
+        <v>0.072035457629624211</v>
       </c>
       <c r="F93" s="1">
-        <v>0.032732860542420347</v>
+        <v>0.032730545506429079</v>
       </c>
       <c r="G93" s="1">
-        <v>0.034336094464019758</v>
+        <v>0.034333507684507721</v>
       </c>
       <c r="H93" s="1">
         <v>0.0012582089552238807</v>
@@ -8084,16 +8078,16 @@
         <v>328</v>
       </c>
       <c r="D94" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E94" s="1">
-        <v>0.084469197185950654</v>
+        <v>0.08449568931569737</v>
       </c>
       <c r="F94" s="1">
-        <v>0.03380647244676864</v>
+        <v>0.033818033653827101</v>
       </c>
       <c r="G94" s="1">
-        <v>0.031576966744561986</v>
+        <v>0.031587619810795352</v>
       </c>
       <c r="H94" s="1">
         <v>0.03450000000000001</v>
@@ -8114,19 +8108,19 @@
         <v>87</v>
       </c>
       <c r="N94" s="1">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O94" s="1">
         <v>93</v>
       </c>
       <c r="P94" s="1">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q94" s="1">
         <v>104</v>
       </c>
       <c r="R94" s="1">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="S94" s="1">
         <v>75</v>
@@ -8149,16 +8143,16 @@
         <v>329</v>
       </c>
       <c r="D95" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E95" s="1">
-        <v>0.12514298181888309</v>
+        <v>0.12517729369398484</v>
       </c>
       <c r="F95" s="1">
-        <v>0.030390532505466909</v>
+        <v>0.030393790745868936</v>
       </c>
       <c r="G95" s="1">
-        <v>0.03153752479614446</v>
+        <v>0.031540760534537443</v>
       </c>
       <c r="H95" s="1">
         <v>0.046028571428571433</v>
@@ -8214,16 +8208,16 @@
         <v>330</v>
       </c>
       <c r="D96" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E96" s="1">
-        <v>0.084469197185950654</v>
+        <v>0.08449568931569737</v>
       </c>
       <c r="F96" s="1">
-        <v>0.03380647244676864</v>
+        <v>0.033818033653827101</v>
       </c>
       <c r="G96" s="1">
-        <v>0.030694079787455301</v>
+        <v>0.030704434995654787</v>
       </c>
       <c r="H96" s="1">
         <v>0.03450000000000001</v>
@@ -8244,19 +8238,19 @@
         <v>88</v>
       </c>
       <c r="N96" s="1">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O96" s="1">
         <v>95</v>
       </c>
       <c r="P96" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q96" s="1">
         <v>103</v>
       </c>
       <c r="R96" s="1">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="S96" s="1">
         <v>87</v>
@@ -8279,16 +8273,16 @@
         <v>331</v>
       </c>
       <c r="D97" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E97" s="1">
-        <v>0.022708712564630314</v>
+        <v>0.022713373420055576</v>
       </c>
       <c r="F97" s="1">
-        <v>0.028555722819044237</v>
+        <v>0.02855054493871689</v>
       </c>
       <c r="G97" s="1">
-        <v>0.030524399749606169</v>
+        <v>0.030518724138112553</v>
       </c>
       <c r="H97" s="1">
         <v>0.024320000000000001</v>
@@ -8344,28 +8338,28 @@
         <v>332</v>
       </c>
       <c r="D98" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E98" s="1">
-        <v>0.072911154437815706</v>
+        <v>0.072936354422272559</v>
       </c>
       <c r="F98" s="1">
-        <v>0.031652005424272545</v>
+        <v>0.031665551248334721</v>
       </c>
       <c r="G98" s="1">
-        <v>0.027374480798180643</v>
+        <v>0.027386069697212093</v>
       </c>
       <c r="H98" s="1">
-        <v>0.012211881188118813</v>
+        <v>0.012211881188118811</v>
       </c>
       <c r="I98" s="1">
-        <v>-0.20071671481481487</v>
+        <v>-0.20071671481481485</v>
       </c>
       <c r="J98" s="1">
         <v>0.19999677473225635</v>
       </c>
       <c r="K98" s="1">
-        <v>0.17617931948894844</v>
+        <v>0.17617931948894841</v>
       </c>
       <c r="L98" s="1">
         <v>0.72406982773191908</v>
@@ -8409,16 +8403,16 @@
         <v>333</v>
       </c>
       <c r="D99" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E99" s="1">
-        <v>0.029766863327854869</v>
+        <v>0.029774715221517506</v>
       </c>
       <c r="F99" s="1">
-        <v>0.022417822170161566</v>
+        <v>0.022418971911686979</v>
       </c>
       <c r="G99" s="1">
-        <v>0.023734114749310063</v>
+        <v>0.023735222526769448</v>
       </c>
       <c r="H99" s="1">
         <v>0.1328</v>
@@ -8474,16 +8468,16 @@
         <v>334</v>
       </c>
       <c r="D100" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E100" s="1">
-        <v>0.031204020623076631</v>
+        <v>0.031208056351342082</v>
       </c>
       <c r="F100" s="1">
-        <v>0.025807830832576751</v>
+        <v>0.025806498723865503</v>
       </c>
       <c r="G100" s="1">
-        <v>0.02314467260240162</v>
+        <v>0.023143371213552342</v>
       </c>
       <c r="H100" s="1">
         <v>0</v>
@@ -8510,7 +8504,7 @@
         <v>99</v>
       </c>
       <c r="P100" s="1">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="Q100" s="1">
         <v>105</v>
@@ -8519,7 +8513,7 @@
         <v>112</v>
       </c>
       <c r="S100" s="1">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="T100" s="1">
         <v>60</v>
@@ -8539,16 +8533,16 @@
         <v>335</v>
       </c>
       <c r="D101" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E101" s="1">
-        <v>0.023783525579642636</v>
+        <v>0.023790275786119391</v>
       </c>
       <c r="F101" s="1">
-        <v>0.023942456179412739</v>
+        <v>0.023945518396390815</v>
       </c>
       <c r="G101" s="1">
-        <v>0.022556222784177172</v>
+        <v>0.022559003655570165</v>
       </c>
       <c r="H101" s="1">
         <v>0</v>
@@ -8566,25 +8560,25 @@
         <v>0.028173672334735882</v>
       </c>
       <c r="M101" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N101" s="1">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="O101" s="1">
         <v>100</v>
       </c>
       <c r="P101" s="1">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="Q101" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R101" s="1">
         <v>96</v>
       </c>
       <c r="S101" s="1">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="T101" s="1">
         <v>122</v>
@@ -8604,25 +8598,25 @@
         <v>336</v>
       </c>
       <c r="D102" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E102" s="1">
-        <v>0.023783525579642636</v>
+        <v>0.023790275786119391</v>
       </c>
       <c r="F102" s="1">
-        <v>0.023942456179412739</v>
+        <v>0.023945518396390815</v>
       </c>
       <c r="G102" s="1">
-        <v>0.022006766337451963</v>
+        <v>0.022009479468437836</v>
       </c>
       <c r="H102" s="1">
         <v>0.030780000000000002</v>
       </c>
       <c r="I102" s="1">
-        <v>-0.54958611000000002</v>
+        <v>-0.54958611000000013</v>
       </c>
       <c r="J102" s="1">
-        <v>0.12181818181818183</v>
+        <v>0.12181818181818184</v>
       </c>
       <c r="K102" s="1">
         <v>0.052111118274861236</v>
@@ -8631,10 +8625,10 @@
         <v>0.051755795889941905</v>
       </c>
       <c r="M102" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N102" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O102" s="1">
         <v>101</v>
@@ -8669,16 +8663,16 @@
         <v>337</v>
       </c>
       <c r="D103" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E103" s="1">
-        <v>0.023783525579642636</v>
+        <v>0.023790275786119391</v>
       </c>
       <c r="F103" s="1">
-        <v>0.023942456179412739</v>
+        <v>0.023945518396390815</v>
       </c>
       <c r="G103" s="1">
-        <v>0.021986727597817692</v>
+        <v>0.021989438258303153</v>
       </c>
       <c r="H103" s="1">
         <v>0</v>
@@ -8696,25 +8690,25 @@
         <v>0.040462303777808281</v>
       </c>
       <c r="M103" s="1">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N103" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O103" s="1">
         <v>102</v>
       </c>
       <c r="P103" s="1">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="Q103" s="1">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R103" s="1">
         <v>97</v>
       </c>
       <c r="S103" s="1">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="T103" s="1">
         <v>117</v>
@@ -8734,16 +8728,16 @@
         <v>338</v>
       </c>
       <c r="D104" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E104" s="1">
-        <v>0.11047555500531951</v>
+        <v>0.11049575290012106</v>
       </c>
       <c r="F104" s="1">
-        <v>0.015757280799870477</v>
+        <v>0.01575321212115903</v>
       </c>
       <c r="G104" s="1">
-        <v>0.020094469005879811</v>
+        <v>0.020089187767937298</v>
       </c>
       <c r="H104" s="1">
         <v>0</v>
@@ -8770,7 +8764,7 @@
         <v>103</v>
       </c>
       <c r="P104" s="1">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="Q104" s="1">
         <v>92</v>
@@ -8779,7 +8773,7 @@
         <v>121</v>
       </c>
       <c r="S104" s="1">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="T104" s="1">
         <v>46</v>
@@ -8799,16 +8793,16 @@
         <v>339</v>
       </c>
       <c r="D105" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E105" s="1">
-        <v>0.11732186242333037</v>
+        <v>0.11735318683412357</v>
       </c>
       <c r="F105" s="1">
-        <v>0.016136327806007423</v>
+        <v>0.01613735377975091</v>
       </c>
       <c r="G105" s="1">
-        <v>0.016997064090238212</v>
+        <v>0.016998066391718348</v>
       </c>
       <c r="H105" s="1">
         <v>0.15382500000000002</v>
@@ -8864,16 +8858,16 @@
         <v>340</v>
       </c>
       <c r="D106" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E106" s="1">
-        <v>0.020528789381796642</v>
+        <v>0.020533734444312612</v>
       </c>
       <c r="F106" s="1">
-        <v>0.01557453818402769</v>
+        <v>0.015573973668590419</v>
       </c>
       <c r="G106" s="1">
-        <v>0.01576228521732196</v>
+        <v>0.015761641200229822</v>
       </c>
       <c r="H106" s="1">
         <v>0</v>
@@ -8900,7 +8894,7 @@
         <v>105</v>
       </c>
       <c r="P106" s="1">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="Q106" s="1">
         <v>55</v>
@@ -8929,16 +8923,16 @@
         <v>341</v>
       </c>
       <c r="D107" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E107" s="1">
-        <v>0.038832997133127517</v>
+        <v>0.038838019550132608</v>
       </c>
       <c r="F107" s="1">
-        <v>0.011586767759501106</v>
+        <v>0.011581406301636524</v>
       </c>
       <c r="G107" s="1">
-        <v>0.012782247234549205</v>
+        <v>0.012776273674144516</v>
       </c>
       <c r="H107" s="1">
         <v>0</v>
@@ -8965,7 +8959,7 @@
         <v>106</v>
       </c>
       <c r="P107" s="1">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="Q107" s="1">
         <v>93</v>
@@ -8994,16 +8988,16 @@
         <v>342</v>
       </c>
       <c r="D108" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E108" s="1">
-        <v>0.13146519715831945</v>
+        <v>0.13150513069217926</v>
       </c>
       <c r="F108" s="1">
-        <v>0.012331537060590191</v>
+        <v>0.012334054281302485</v>
       </c>
       <c r="G108" s="1">
-        <v>0.012759304902434439</v>
+        <v>0.012761850582048316</v>
       </c>
       <c r="H108" s="1">
         <v>0.0041266666666666665</v>
@@ -9059,16 +9053,16 @@
         <v>343</v>
       </c>
       <c r="D109" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E109" s="1">
-        <v>0.027173811285548091</v>
+        <v>0.027180908024692405</v>
       </c>
       <c r="F109" s="1">
-        <v>0.011843740752057137</v>
+        <v>0.011843288718131935</v>
       </c>
       <c r="G109" s="1">
-        <v>0.011569990764207288</v>
+        <v>0.011569495816995011</v>
       </c>
       <c r="H109" s="1">
         <v>0.051650000000000008</v>
@@ -9124,31 +9118,31 @@
         <v>344</v>
       </c>
       <c r="D110" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E110" s="1">
-        <v>0.028427238469859024</v>
+        <v>0.028435970104488222</v>
       </c>
       <c r="F110" s="1">
-        <v>0.011156204477202201</v>
+        <v>0.011158412783922787</v>
       </c>
       <c r="G110" s="1">
-        <v>0.010572485785012051</v>
+        <v>0.01057452977563079</v>
       </c>
       <c r="H110" s="1">
-        <v>0.027266666666666675</v>
+        <v>0.027266666666666672</v>
       </c>
       <c r="I110" s="1">
-        <v>-0.8380786968055558</v>
+        <v>-0.83807869680555558</v>
       </c>
       <c r="J110" s="1">
-        <v>0.17774059340793774</v>
+        <v>0.17774059340793771</v>
       </c>
       <c r="K110" s="1">
         <v>0.060012942270963189</v>
       </c>
       <c r="L110" s="1">
-        <v>0.098171312462841956</v>
+        <v>0.098171312462841928</v>
       </c>
       <c r="M110" s="1">
         <v>105</v>
@@ -9189,16 +9183,16 @@
         <v>345</v>
       </c>
       <c r="D111" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E111" s="1">
-        <v>0.010229982446653596</v>
+        <v>0.010232751186075379</v>
       </c>
       <c r="F111" s="1">
-        <v>0.0059590170907038624</v>
+        <v>0.0059596519551888549</v>
       </c>
       <c r="G111" s="1">
-        <v>0.0078895879320787406</v>
+        <v>0.0078903920841723353</v>
       </c>
       <c r="H111" s="1">
         <v>0.042499999999999996</v>
@@ -9216,10 +9210,10 @@
         <v>0.36346695645395394</v>
       </c>
       <c r="M111" s="1">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="N111" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O111" s="1">
         <v>110</v>
@@ -9254,16 +9248,16 @@
         <v>346</v>
       </c>
       <c r="D112" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E112" s="1">
-        <v>0.029660393010508587</v>
+        <v>0.029666580137575352</v>
       </c>
       <c r="F112" s="1">
-        <v>0.0080730276516788029</v>
+        <v>0.0080717385648337754</v>
       </c>
       <c r="G112" s="1">
-        <v>0.0071828959839631218</v>
+        <v>0.0071817159079352287</v>
       </c>
       <c r="H112" s="1">
         <v>0.089599999999999999</v>
@@ -9319,16 +9313,16 @@
         <v>347</v>
       </c>
       <c r="D113" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E113" s="1">
-        <v>0.036398133295258317</v>
+        <v>0.036405344243383181</v>
       </c>
       <c r="F113" s="1">
-        <v>0.0047301539731102581</v>
+        <v>0.004729863353249741</v>
       </c>
       <c r="G113" s="1">
-        <v>0.0056196999005576481</v>
+        <v>0.0056193287094191552</v>
       </c>
       <c r="H113" s="1">
         <v>0.10666</v>
@@ -9349,7 +9343,7 @@
         <v>101</v>
       </c>
       <c r="N113" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O113" s="1">
         <v>112</v>
@@ -9384,58 +9378,58 @@
         <v>348</v>
       </c>
       <c r="D114" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E114" s="1">
-        <v>0.014840990086867973</v>
+        <v>0.006584132449516558</v>
       </c>
       <c r="F114" s="1">
-        <v>0.0059877954165750832</v>
+        <v>0.0046771099132538307</v>
       </c>
       <c r="G114" s="1">
-        <v>0.0052964286956197872</v>
+        <v>0.0047737988521817688</v>
       </c>
       <c r="H114" s="1">
-        <v>0.012230000000000001</v>
+        <v>0.023399999999999997</v>
       </c>
       <c r="I114" s="1">
-        <v>-1.052960195</v>
+        <v>-0.027789766666666646</v>
       </c>
       <c r="J114" s="1">
-        <v>0.099853537313846663</v>
+        <v>0.33080602679845056</v>
       </c>
       <c r="K114" s="1">
-        <v>0.022490331523592449</v>
+        <v>0.024650155582156351</v>
       </c>
       <c r="L114" s="1">
-        <v>0.046080581978055604</v>
+        <v>0.087450504899540232</v>
       </c>
       <c r="M114" s="1">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="N114" s="1">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O114" s="1">
         <v>113</v>
       </c>
       <c r="P114" s="1">
+        <v>83</v>
+      </c>
+      <c r="Q114" s="1">
+        <v>82</v>
+      </c>
+      <c r="R114" s="1">
+        <v>71</v>
+      </c>
+      <c r="S114" s="1">
         <v>99</v>
       </c>
-      <c r="Q114" s="1">
-        <v>125</v>
-      </c>
-      <c r="R114" s="1">
-        <v>124</v>
-      </c>
-      <c r="S114" s="1">
-        <v>101</v>
-      </c>
       <c r="T114" s="1">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="U114" s="1">
-        <v>39479.61599999998</v>
+        <v>22615.559000000001</v>
       </c>
     </row>
     <row r="115">
@@ -9449,58 +9443,58 @@
         <v>349</v>
       </c>
       <c r="D115" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E115" s="1">
-        <v>0.0065832121532733313</v>
+        <v>0.01473207888946977</v>
       </c>
       <c r="F115" s="1">
-        <v>0.0046794692556336101</v>
+        <v>0.0044203710312074361</v>
       </c>
       <c r="G115" s="1">
-        <v>0.004776228997806828</v>
+        <v>0.0040661341263394978</v>
       </c>
       <c r="H115" s="1">
-        <v>0.023399999999999994</v>
+        <v>0.01131764705882353</v>
       </c>
       <c r="I115" s="1">
-        <v>-0.02778976666666666</v>
+        <v>-0.36410772222222221</v>
       </c>
       <c r="J115" s="1">
-        <v>0.33080602679845061</v>
+        <v>0.22363061656001465</v>
       </c>
       <c r="K115" s="1">
-        <v>0.024650155582156347</v>
+        <v>0.010777492096230374</v>
       </c>
       <c r="L115" s="1">
-        <v>0.087450504899540246</v>
+        <v>0.053441412533876818</v>
       </c>
       <c r="M115" s="1">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="N115" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O115" s="1">
         <v>114</v>
       </c>
       <c r="P115" s="1">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="Q115" s="1">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="R115" s="1">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="S115" s="1">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="T115" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="U115" s="1">
-        <v>22615.559000000001</v>
+        <v>20443.963000000003</v>
       </c>
     </row>
     <row r="116">
@@ -9514,58 +9508,58 @@
         <v>350</v>
       </c>
       <c r="D116" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E116" s="1">
-        <v>0.014726331019123363</v>
+        <v>0.015167635011964145</v>
       </c>
       <c r="F116" s="1">
-        <v>0.0044190894064536574</v>
+        <v>0.0046452658188512047</v>
       </c>
       <c r="G116" s="1">
-        <v>0.004064973956195198</v>
+        <v>0.0039852179578264493</v>
       </c>
       <c r="H116" s="1">
-        <v>0.01131764705882353</v>
+        <v>0.010150000000000003</v>
       </c>
       <c r="I116" s="1">
-        <v>-0.36410772222222221</v>
+        <v>-0.94952243000000036</v>
       </c>
       <c r="J116" s="1">
-        <v>0.22363061656001465</v>
+        <v>0.085072834966452002</v>
       </c>
       <c r="K116" s="1">
-        <v>0.010777492096230374</v>
+        <v>0.077600291807107369</v>
       </c>
       <c r="L116" s="1">
-        <v>0.053441412533876818</v>
+        <v>0.16321997927428714</v>
       </c>
       <c r="M116" s="1">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="N116" s="1">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="O116" s="1">
         <v>115</v>
       </c>
       <c r="P116" s="1">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q116" s="1">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="R116" s="1">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="S116" s="1">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="T116" s="1">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="U116" s="1">
-        <v>20443.963000000003</v>
+        <v>164134.86100000018</v>
       </c>
     </row>
     <row r="117">
@@ -9579,58 +9573,58 @@
         <v>351</v>
       </c>
       <c r="D117" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E117" s="1">
-        <v>0.015158832323227326</v>
+        <v>0.0051163755930376895</v>
       </c>
       <c r="F117" s="1">
-        <v>0.0046394066415022519</v>
+        <v>0.0029798259775944275</v>
       </c>
       <c r="G117" s="1">
-        <v>0.0039802096711827554</v>
+        <v>0.0031357149381780972</v>
       </c>
       <c r="H117" s="1">
-        <v>0.010150000000000003</v>
+        <v>0.016737500000000002</v>
       </c>
       <c r="I117" s="1">
-        <v>-0.94952243000000025</v>
+        <v>-0.21339948055555558</v>
       </c>
       <c r="J117" s="1">
-        <v>0.085072834966452002</v>
+        <v>0.21742045749153804</v>
       </c>
       <c r="K117" s="1">
-        <v>0.077600291807107369</v>
+        <v>0.017430027485138333</v>
       </c>
       <c r="L117" s="1">
-        <v>0.16321997927428714</v>
+        <v>0.056818921757663413</v>
       </c>
       <c r="M117" s="1">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="N117" s="1">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="O117" s="1">
         <v>116</v>
       </c>
       <c r="P117" s="1">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="Q117" s="1">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="R117" s="1">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="S117" s="1">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="T117" s="1">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="U117" s="1">
-        <v>164134.86100000018</v>
+        <v>22356.870000000003</v>
       </c>
     </row>
     <row r="118">
@@ -9644,58 +9638,58 @@
         <v>352</v>
       </c>
       <c r="D118" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E118" s="1">
-        <v>0.0051149912233267982</v>
+        <v>0.01649133130239671</v>
       </c>
       <c r="F118" s="1">
-        <v>0.0029795085453519312</v>
+        <v>0.0029902416773621115</v>
       </c>
       <c r="G118" s="1">
-        <v>0.0031353953606836509</v>
+        <v>0.0028459455290330499</v>
       </c>
       <c r="H118" s="1">
-        <v>0.016737500000000002</v>
+        <v>0.00083993174061433465</v>
       </c>
       <c r="I118" s="1">
-        <v>-0.21339948055555563</v>
+        <v>-0.79541918200000006</v>
       </c>
       <c r="J118" s="1">
-        <v>0.21742045749153804</v>
+        <v>0.19078817540794277</v>
       </c>
       <c r="K118" s="1">
-        <v>0.017430027485138333</v>
+        <v>0.0037253026260822644</v>
       </c>
       <c r="L118" s="1">
-        <v>0.056818921757663413</v>
+        <v>0.21235090717500785</v>
       </c>
       <c r="M118" s="1">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="N118" s="1">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="O118" s="1">
         <v>117</v>
       </c>
       <c r="P118" s="1">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="Q118" s="1">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="R118" s="1">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="S118" s="1">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="T118" s="1">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="U118" s="1">
-        <v>22356.870000000003</v>
+        <v>95218.445000000167</v>
       </c>
     </row>
     <row r="119">
@@ -9709,34 +9703,34 @@
         <v>353</v>
       </c>
       <c r="D119" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E119" s="1">
-        <v>0.016490944526818246</v>
+        <v>0.0074177805652226956</v>
       </c>
       <c r="F119" s="1">
-        <v>0.0029910622600757483</v>
+        <v>0.0029868448829538166</v>
       </c>
       <c r="G119" s="1">
-        <v>0.0028467396437721485</v>
+        <v>0.0026419636749862212</v>
       </c>
       <c r="H119" s="1">
-        <v>0.00083993174061433454</v>
+        <v>0.012230000000000003</v>
       </c>
       <c r="I119" s="1">
-        <v>-0.79541918200000017</v>
+        <v>-1.0529601950000003</v>
       </c>
       <c r="J119" s="1">
-        <v>0.19078817540794277</v>
+        <v>0.099853537313846649</v>
       </c>
       <c r="K119" s="1">
-        <v>0.0037253026260822635</v>
+        <v>0.022490331523592449</v>
       </c>
       <c r="L119" s="1">
-        <v>0.21235090717500785</v>
+        <v>0.046080581978055597</v>
       </c>
       <c r="M119" s="1">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="N119" s="1">
         <v>117</v>
@@ -9745,22 +9739,22 @@
         <v>118</v>
       </c>
       <c r="P119" s="1">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="Q119" s="1">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="R119" s="1">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="S119" s="1">
+        <v>101</v>
+      </c>
+      <c r="T119" s="1">
         <v>115</v>
       </c>
-      <c r="T119" s="1">
-        <v>80</v>
-      </c>
       <c r="U119" s="1">
-        <v>95218.445000000167</v>
+        <v>39479.61599999998</v>
       </c>
     </row>
     <row r="120">
@@ -9771,37 +9765,37 @@
         <v>249</v>
       </c>
       <c r="C120" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D120" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E120" s="1">
-        <v>0.014840990086867973</v>
+        <v>0.0032303127532323913</v>
       </c>
       <c r="F120" s="1">
-        <v>0.0022959239766550347</v>
+        <v>0.002199264688888172</v>
       </c>
       <c r="G120" s="1">
-        <v>0.0021388212208839023</v>
+        <v>0.0019542196478829188</v>
       </c>
       <c r="H120" s="1">
-        <v>0.013066666666666664</v>
+        <v>0.0058458598726114658</v>
       </c>
       <c r="I120" s="1">
-        <v>-0.73658427999999998</v>
+        <v>-0.63639752235507252</v>
       </c>
       <c r="J120" s="1">
-        <v>0.11203885003885003</v>
+        <v>0.29466701687054203</v>
       </c>
       <c r="K120" s="1">
-        <v>0.10557926179172081</v>
+        <v>0.27554054897943692</v>
       </c>
       <c r="L120" s="1">
-        <v>0.22717866973595763</v>
+        <v>3.4854089784941431</v>
       </c>
       <c r="M120" s="1">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="N120" s="1">
         <v>119</v>
@@ -9810,22 +9804,22 @@
         <v>119</v>
       </c>
       <c r="P120" s="1">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="Q120" s="1">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="R120" s="1">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="S120" s="1">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="T120" s="1">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="U120" s="1">
-        <v>173467.18400000012</v>
+        <v>1011907.0879999916</v>
       </c>
     </row>
     <row r="121">
@@ -9839,58 +9833,58 @@
         <v>354</v>
       </c>
       <c r="D121" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E121" s="1">
-        <v>0.0032292889294450993</v>
+        <v>0.0021904118227164806</v>
       </c>
       <c r="F121" s="1">
-        <v>0.0021987041908734474</v>
+        <v>0.0014563964870415152</v>
       </c>
       <c r="G121" s="1">
-        <v>0.0019537306123584707</v>
+        <v>0.0018713019115793351</v>
       </c>
       <c r="H121" s="1">
-        <v>0.0058458598726114667</v>
+        <v>0</v>
       </c>
       <c r="I121" s="1">
-        <v>-0.63639752235507252</v>
+        <v>0.55739609999999995</v>
       </c>
       <c r="J121" s="1">
-        <v>0.29466701687054192</v>
+        <v>0.39285714285714285</v>
       </c>
       <c r="K121" s="1">
-        <v>0.27554054897943692</v>
+        <v>0</v>
       </c>
       <c r="L121" s="1">
-        <v>3.4854089784941413</v>
+        <v>0.017844178838325474</v>
       </c>
       <c r="M121" s="1">
+        <v>125</v>
+      </c>
+      <c r="N121" s="1">
         <v>122</v>
-      </c>
-      <c r="N121" s="1">
-        <v>120</v>
       </c>
       <c r="O121" s="1">
         <v>120</v>
       </c>
       <c r="P121" s="1">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Q121" s="1">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="R121" s="1">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="S121" s="1">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="T121" s="1">
-        <v>7</v>
+        <v>126</v>
       </c>
       <c r="U121" s="1">
-        <v>1011907.0879999916</v>
+        <v>3885.7989999999991</v>
       </c>
     </row>
     <row r="122">
@@ -9904,58 +9898,58 @@
         <v>355</v>
       </c>
       <c r="D122" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E122" s="1">
-        <v>0.0021895479404196883</v>
+        <v>0.0024379718892319933</v>
       </c>
       <c r="F122" s="1">
-        <v>0.0014555941094726538</v>
+        <v>0.0016598224067080542</v>
       </c>
       <c r="G122" s="1">
-        <v>0.0018702795748753913</v>
+        <v>0.0015235983187064503</v>
       </c>
       <c r="H122" s="1">
         <v>0</v>
       </c>
       <c r="I122" s="1">
-        <v>0.55739609999999995</v>
+        <v>-0.73650196349206332</v>
       </c>
       <c r="J122" s="1">
-        <v>0.39285714285714285</v>
+        <v>0.23865485448020371</v>
       </c>
       <c r="K122" s="1">
         <v>0</v>
       </c>
       <c r="L122" s="1">
-        <v>0.017844178838325474</v>
+        <v>0.037151985387571147</v>
       </c>
       <c r="M122" s="1">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N122" s="1">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O122" s="1">
         <v>121</v>
       </c>
       <c r="P122" s="1">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Q122" s="1">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="R122" s="1">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="S122" s="1">
         <v>126</v>
       </c>
       <c r="T122" s="1">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="U122" s="1">
-        <v>3885.7989999999991</v>
+        <v>13317.728999999998</v>
       </c>
     </row>
     <row r="123">
@@ -9966,61 +9960,61 @@
         <v>252</v>
       </c>
       <c r="C123" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D123" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E123" s="1">
-        <v>0.0024371991920340372</v>
+        <v>0.0024379718892319933</v>
       </c>
       <c r="F123" s="1">
-        <v>0.001659399389338451</v>
+        <v>0.0016598224067080542</v>
       </c>
       <c r="G123" s="1">
-        <v>0.0015232170444194764</v>
+        <v>0.0015202945832718472</v>
       </c>
       <c r="H123" s="1">
-        <v>0</v>
+        <v>0.0095230769230769223</v>
       </c>
       <c r="I123" s="1">
-        <v>-0.73650196349206354</v>
+        <v>-0.68810868833333338</v>
       </c>
       <c r="J123" s="1">
-        <v>0.23865485448020371</v>
+        <v>0.17332848176318885</v>
       </c>
       <c r="K123" s="1">
-        <v>0</v>
+        <v>0.061837062299271633</v>
       </c>
       <c r="L123" s="1">
-        <v>0.037151985387571147</v>
+        <v>0.28244025221039465</v>
       </c>
       <c r="M123" s="1">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="N123" s="1">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O123" s="1">
         <v>122</v>
       </c>
       <c r="P123" s="1">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="Q123" s="1">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="R123" s="1">
+        <v>109</v>
+      </c>
+      <c r="S123" s="1">
         <v>88</v>
       </c>
-      <c r="S123" s="1">
-        <v>127</v>
-      </c>
       <c r="T123" s="1">
-        <v>119</v>
+        <v>66</v>
       </c>
       <c r="U123" s="1">
-        <v>13317.728999999998</v>
+        <v>139403.94899999979</v>
       </c>
     </row>
     <row r="124">
@@ -10031,61 +10025,61 @@
         <v>253</v>
       </c>
       <c r="C124" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D124" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E124" s="1">
-        <v>0.0024371991920340372</v>
+        <v>0.0074177805652226973</v>
       </c>
       <c r="F124" s="1">
-        <v>0.001659399389338451</v>
+        <v>0.0011452576957356165</v>
       </c>
       <c r="G124" s="1">
-        <v>0.0015199141357312381</v>
+        <v>0.0010668864432250623</v>
       </c>
       <c r="H124" s="1">
-        <v>0.0095230769230769223</v>
+        <v>0.013066666666666664</v>
       </c>
       <c r="I124" s="1">
-        <v>-0.68810868833333338</v>
+        <v>-0.73658427999999998</v>
       </c>
       <c r="J124" s="1">
-        <v>0.17332848176318885</v>
+        <v>0.11203885003885003</v>
       </c>
       <c r="K124" s="1">
-        <v>0.061837062299271633</v>
+        <v>0.10557926179172081</v>
       </c>
       <c r="L124" s="1">
-        <v>0.28244025221039465</v>
+        <v>0.22717866973595763</v>
       </c>
       <c r="M124" s="1">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="N124" s="1">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O124" s="1">
         <v>123</v>
       </c>
       <c r="P124" s="1">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="Q124" s="1">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="R124" s="1">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="S124" s="1">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="T124" s="1">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="U124" s="1">
-        <v>139403.94899999979</v>
+        <v>173467.18400000012</v>
       </c>
     </row>
     <row r="125">
@@ -10096,19 +10090,19 @@
         <v>254</v>
       </c>
       <c r="C125" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D125" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E125" s="1">
-        <v>0.0016451094546229748</v>
+        <v>0.0016456310252315955</v>
       </c>
       <c r="F125" s="1">
-        <v>0.0011200945878034542</v>
+        <v>0.0011203801245279368</v>
       </c>
       <c r="G125" s="1">
-        <v>0.0010027283850713444</v>
+        <v>0.0010029793765839771</v>
       </c>
       <c r="H125" s="1">
         <v>0.031584122562674101</v>
@@ -10117,16 +10111,16 @@
         <v>-0.74153786351405648</v>
       </c>
       <c r="J125" s="1">
-        <v>0.25446163069508559</v>
+        <v>0.25446163069508554</v>
       </c>
       <c r="K125" s="1">
         <v>0.65930896393549054</v>
       </c>
       <c r="L125" s="1">
-        <v>1.3329920857267312</v>
+        <v>1.3329920857267308</v>
       </c>
       <c r="M125" s="1">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N125" s="1">
         <v>124</v>
@@ -10161,19 +10155,19 @@
         <v>255</v>
       </c>
       <c r="C126" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D126" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E126" s="1">
-        <v>0.0095789126020273379</v>
+        <v>0.0047877042784468544</v>
       </c>
       <c r="F126" s="1">
-        <v>0.0007842491782061639</v>
+        <v>0.00039120084804528061</v>
       </c>
       <c r="G126" s="1">
-        <v>0.00088419114917926409</v>
+        <v>0.0004410520809631292</v>
       </c>
       <c r="H126" s="1">
         <v>0</v>
@@ -10191,7 +10185,7 @@
         <v>2.1296681279392993</v>
       </c>
       <c r="M126" s="1">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N126" s="1">
         <v>125</v>
@@ -10200,7 +10194,7 @@
         <v>125</v>
       </c>
       <c r="P126" s="1">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q126" s="1">
         <v>121</v>
@@ -10209,7 +10203,7 @@
         <v>118</v>
       </c>
       <c r="S126" s="1">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="T126" s="1">
         <v>12</v>
@@ -10226,19 +10220,19 @@
         <v>256</v>
       </c>
       <c r="C127" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D127" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E127" s="1">
-        <v>0.0086210213418246012</v>
+        <v>0.0043089338506021686</v>
       </c>
       <c r="F127" s="1">
-        <v>0.00070582426038554751</v>
+        <v>0.0003520807632407525</v>
       </c>
       <c r="G127" s="1">
-        <v>0.00071994778210182869</v>
+        <v>0.00035912423210246702</v>
       </c>
       <c r="H127" s="1">
         <v>0</v>
@@ -10256,7 +10250,7 @@
         <v>0.14116266904407826</v>
       </c>
       <c r="M127" s="1">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N127" s="1">
         <v>126</v>
@@ -10265,7 +10259,7 @@
         <v>126</v>
       </c>
       <c r="P127" s="1">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="Q127" s="1">
         <v>118</v>
@@ -10274,7 +10268,7 @@
         <v>104</v>
       </c>
       <c r="S127" s="1">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="T127" s="1">
         <v>95</v>
@@ -10291,19 +10285,19 @@
         <v>257</v>
       </c>
       <c r="C128" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D128" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E128" s="1">
-        <v>0.0028736737806082007</v>
+        <v>0.0014363112835340561</v>
       </c>
       <c r="F128" s="1">
-        <v>0.00023527475346184914</v>
+        <v>0.00011736025441358418</v>
       </c>
       <c r="G128" s="1">
-        <v>0.00025676709808681767</v>
+        <v>0.00012808052086833843</v>
       </c>
       <c r="H128" s="1">
         <v>0</v>
@@ -10321,7 +10315,7 @@
         <v>0.012828636807316706</v>
       </c>
       <c r="M128" s="1">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="N128" s="1">
         <v>127</v>
@@ -10330,7 +10324,7 @@
         <v>127</v>
       </c>
       <c r="P128" s="1">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="Q128" s="1">
         <v>126</v>
@@ -10339,7 +10333,7 @@
         <v>116</v>
       </c>
       <c r="S128" s="1">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="T128" s="1">
         <v>127</v>
@@ -10356,19 +10350,19 @@
         <v>258</v>
       </c>
       <c r="C129" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D129" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E129" s="1">
-        <v>0.0014749880228173572</v>
+        <v>0.00073722423002438981</v>
       </c>
       <c r="F129" s="1">
-        <v>0.00016841696118320151</v>
+        <v>8.4010107847072137e-05</v>
       </c>
       <c r="G129" s="1">
-        <v>0.00020838151144468166</v>
+        <v>0.00010394483064236757</v>
       </c>
       <c r="H129" s="1">
         <v>0</v>
@@ -10395,7 +10389,7 @@
         <v>128</v>
       </c>
       <c r="P129" s="1">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="Q129" s="1">
         <v>115</v>
@@ -10404,7 +10398,7 @@
         <v>129</v>
       </c>
       <c r="S129" s="1">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="T129" s="1">
         <v>124</v>
@@ -10421,31 +10415,31 @@
         <v>259</v>
       </c>
       <c r="C130" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D130" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E130" s="1">
-        <v>0.00073749401140867858</v>
+        <v>0.0003686121150121949</v>
       </c>
       <c r="F130" s="1">
-        <v>8.4208480591600754e-05</v>
+        <v>4.2005053923536069e-05</v>
       </c>
       <c r="G130" s="1">
-        <v>6.9651735323373549e-05</v>
+        <v>3.4743666949824554e-05</v>
       </c>
       <c r="H130" s="1">
-        <v>0.012262295081967212</v>
+        <v>0.01226229508196721</v>
       </c>
       <c r="I130" s="1">
         <v>-0.54986195409836069</v>
       </c>
       <c r="J130" s="1">
-        <v>0.18063126007206814</v>
+        <v>0.18063126007206812</v>
       </c>
       <c r="K130" s="1">
-        <v>0.46451320046027483</v>
+        <v>0.46451320046027478</v>
       </c>
       <c r="L130" s="1">
         <v>1.717134482992013</v>
@@ -10489,132 +10483,132 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D1" t="s">
         <v>488</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>489</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>490</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>491</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>492</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>493</v>
-      </c>
-      <c r="H1" t="s">
-        <v>494</v>
-      </c>
-      <c r="I1" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>0.96284735202789307</v>
+        <v>0.96315348148345947</v>
       </c>
       <c r="D2" s="1">
-        <v>0.96187490224838257</v>
+        <v>0.96214187145233154</v>
       </c>
       <c r="E2" s="1">
-        <v>0.69551765918731689</v>
+        <v>0.69697654247283936</v>
       </c>
       <c r="F2" s="1">
-        <v>0.59805089235305786</v>
+        <v>0.60031974315643311</v>
       </c>
       <c r="G2" s="1">
-        <v>0.68475818634033203</v>
+        <v>0.68672502040863037</v>
       </c>
       <c r="H2" s="1">
-        <v>0.55031335353851318</v>
+        <v>0.55177521705627441</v>
       </c>
       <c r="I2" s="1">
-        <v>0.29213166236877441</v>
+        <v>0.29234090447425842</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B3" s="1">
-        <v>0.96284735202789307</v>
+        <v>0.96315348148345947</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>0.99868065118789673</v>
+        <v>0.9986918568611145</v>
       </c>
       <c r="E3" s="1">
-        <v>0.69021427631378174</v>
+        <v>0.6902422308921814</v>
       </c>
       <c r="F3" s="1">
-        <v>0.62554925680160522</v>
+        <v>0.62692451477050781</v>
       </c>
       <c r="G3" s="1">
-        <v>0.69930344820022583</v>
+        <v>0.70107561349868774</v>
       </c>
       <c r="H3" s="1">
-        <v>0.50089919567108154</v>
+        <v>0.500865638256073</v>
       </c>
       <c r="I3" s="1">
-        <v>0.21389658749103546</v>
+        <v>0.21464011073112488</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B4" s="1">
-        <v>0.96187490224838257</v>
+        <v>0.96214187145233154</v>
       </c>
       <c r="C4" s="1">
-        <v>0.99868065118789673</v>
+        <v>0.9986918568611145</v>
       </c>
       <c r="D4" s="1">
         <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>0.68947297334671021</v>
+        <v>0.68908149003982544</v>
       </c>
       <c r="F4" s="1">
-        <v>0.62519741058349609</v>
+        <v>0.62630987167358398</v>
       </c>
       <c r="G4" s="1">
-        <v>0.69490915536880493</v>
+        <v>0.69648003578186035</v>
       </c>
       <c r="H4" s="1">
-        <v>0.50488013029098511</v>
+        <v>0.50442707538604736</v>
       </c>
       <c r="I4" s="1">
-        <v>0.21958296000957489</v>
+        <v>0.22003577649593353</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B5" s="1">
-        <v>0.69551765918731689</v>
+        <v>0.69697654247283936</v>
       </c>
       <c r="C5" s="1">
-        <v>0.69021427631378174</v>
+        <v>0.6902422308921814</v>
       </c>
       <c r="D5" s="1">
-        <v>0.68947297334671021</v>
+        <v>0.68908149003982544</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -10634,16 +10628,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B6" s="1">
-        <v>0.59805089235305786</v>
+        <v>0.60031974315643311</v>
       </c>
       <c r="C6" s="1">
-        <v>0.62554925680160522</v>
+        <v>0.62692451477050781</v>
       </c>
       <c r="D6" s="1">
-        <v>0.62519741058349609</v>
+        <v>0.62630987167358398</v>
       </c>
       <c r="E6" s="1">
         <v>0.80931222438812256</v>
@@ -10663,16 +10657,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B7" s="1">
-        <v>0.68475818634033203</v>
+        <v>0.68672502040863037</v>
       </c>
       <c r="C7" s="1">
-        <v>0.69930344820022583</v>
+        <v>0.70107561349868774</v>
       </c>
       <c r="D7" s="1">
-        <v>0.69490915536880493</v>
+        <v>0.69648003578186035</v>
       </c>
       <c r="E7" s="1">
         <v>0.84288829565048218</v>
@@ -10692,16 +10686,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B8" s="1">
-        <v>0.55031335353851318</v>
+        <v>0.55177521705627441</v>
       </c>
       <c r="C8" s="1">
-        <v>0.50089919567108154</v>
+        <v>0.500865638256073</v>
       </c>
       <c r="D8" s="1">
-        <v>0.50488013029098511</v>
+        <v>0.50442707538604736</v>
       </c>
       <c r="E8" s="1">
         <v>0.75725632905960083</v>
@@ -10721,16 +10715,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B9" s="1">
-        <v>0.29213166236877441</v>
+        <v>0.29234090447425842</v>
       </c>
       <c r="C9" s="1">
-        <v>0.21389658749103546</v>
+        <v>0.21464011073112488</v>
       </c>
       <c r="D9" s="1">
-        <v>0.21958296000957489</v>
+        <v>0.22003577649593353</v>
       </c>
       <c r="E9" s="1">
         <v>0.30428093671798706</v>
@@ -10759,132 +10753,132 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C1" t="s">
+        <v>504</v>
+      </c>
+      <c r="D1" t="s">
         <v>505</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>506</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>507</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>508</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>509</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>510</v>
-      </c>
-      <c r="H1" t="s">
-        <v>511</v>
-      </c>
-      <c r="I1" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>0.96241980791091919</v>
+        <v>0.96241873502731323</v>
       </c>
       <c r="D2" s="1">
-        <v>0.96376156806945801</v>
+        <v>0.96375983953475952</v>
       </c>
       <c r="E2" s="1">
-        <v>0.57306897640228271</v>
+        <v>0.57313883304595947</v>
       </c>
       <c r="F2" s="1">
-        <v>0.31354218721389771</v>
+        <v>0.31369763612747192</v>
       </c>
       <c r="G2" s="1">
-        <v>0.49797657132148743</v>
+        <v>0.49810570478439331</v>
       </c>
       <c r="H2" s="1">
-        <v>0.30263453722000122</v>
+        <v>0.30267494916915894</v>
       </c>
       <c r="I2" s="1">
-        <v>0.1494051069021225</v>
+        <v>0.14942371845245361</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B3" s="1">
-        <v>0.96241980791091919</v>
+        <v>0.96241873502731323</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>0.99730628728866577</v>
+        <v>0.99730598926544189</v>
       </c>
       <c r="E3" s="1">
-        <v>0.58541810512542725</v>
+        <v>0.58543306589126587</v>
       </c>
       <c r="F3" s="1">
-        <v>0.33740049600601196</v>
+        <v>0.337434321641922</v>
       </c>
       <c r="G3" s="1">
-        <v>0.51615798473358154</v>
+        <v>0.51618468761444092</v>
       </c>
       <c r="H3" s="1">
-        <v>0.30057662725448608</v>
+        <v>0.30058941245079041</v>
       </c>
       <c r="I3" s="1">
-        <v>0.13567517697811127</v>
+        <v>0.1356867253780365</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B4" s="1">
-        <v>0.96376156806945801</v>
+        <v>0.96375983953475952</v>
       </c>
       <c r="C4" s="1">
-        <v>0.99730628728866577</v>
+        <v>0.99730598926544189</v>
       </c>
       <c r="D4" s="1">
         <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>0.57716923952102661</v>
+        <v>0.57718342542648315</v>
       </c>
       <c r="F4" s="1">
-        <v>0.33842921257019043</v>
+        <v>0.33846172690391541</v>
       </c>
       <c r="G4" s="1">
-        <v>0.50928401947021484</v>
+        <v>0.5093085765838623</v>
       </c>
       <c r="H4" s="1">
-        <v>0.2965272068977356</v>
+        <v>0.29654043912887573</v>
       </c>
       <c r="I4" s="1">
-        <v>0.13671201467514038</v>
+        <v>0.13672368228435516</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B5" s="1">
-        <v>0.57306897640228271</v>
+        <v>0.57313883304595947</v>
       </c>
       <c r="C5" s="1">
-        <v>0.58541810512542725</v>
+        <v>0.58543306589126587</v>
       </c>
       <c r="D5" s="1">
-        <v>0.57716923952102661</v>
+        <v>0.57718342542648315</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -10904,16 +10898,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B6" s="1">
-        <v>0.31354218721389771</v>
+        <v>0.31369763612747192</v>
       </c>
       <c r="C6" s="1">
-        <v>0.33740049600601196</v>
+        <v>0.337434321641922</v>
       </c>
       <c r="D6" s="1">
-        <v>0.33842921257019043</v>
+        <v>0.33846172690391541</v>
       </c>
       <c r="E6" s="1">
         <v>0.70112234354019165</v>
@@ -10933,16 +10927,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B7" s="1">
-        <v>0.49797657132148743</v>
+        <v>0.49810570478439331</v>
       </c>
       <c r="C7" s="1">
-        <v>0.51615798473358154</v>
+        <v>0.51618468761444092</v>
       </c>
       <c r="D7" s="1">
-        <v>0.50928401947021484</v>
+        <v>0.5093085765838623</v>
       </c>
       <c r="E7" s="1">
         <v>0.81782150268554688</v>
@@ -10962,16 +10956,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B8" s="1">
-        <v>0.30263453722000122</v>
+        <v>0.30267494916915894</v>
       </c>
       <c r="C8" s="1">
-        <v>0.30057662725448608</v>
+        <v>0.30058941245079041</v>
       </c>
       <c r="D8" s="1">
-        <v>0.2965272068977356</v>
+        <v>0.29654043912887573</v>
       </c>
       <c r="E8" s="1">
         <v>0.49886927008628845</v>
@@ -10991,16 +10985,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B9" s="1">
-        <v>0.1494051069021225</v>
+        <v>0.14942371845245361</v>
       </c>
       <c r="C9" s="1">
-        <v>0.13567517697811127</v>
+        <v>0.1356867253780365</v>
       </c>
       <c r="D9" s="1">
-        <v>0.13671201467514038</v>
+        <v>0.13672368228435516</v>
       </c>
       <c r="E9" s="1">
         <v>0.26386091113090515</v>
@@ -11029,36 +11023,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B1" t="s">
+        <v>520</v>
+      </c>
+      <c r="C1" t="s">
+        <v>521</v>
+      </c>
+      <c r="D1" t="s">
         <v>522</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>523</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>524</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>525</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>526</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>527</v>
-      </c>
-      <c r="H1" t="s">
-        <v>528</v>
-      </c>
-      <c r="I1" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B2" s="1">
         <v>30</v>
@@ -11087,7 +11081,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B3" s="1">
         <v>26</v>
@@ -11116,7 +11110,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B4" s="1">
         <v>26</v>
@@ -11145,7 +11139,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B5" s="1">
         <v>18</v>
@@ -11174,7 +11168,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B6" s="1">
         <v>15</v>
@@ -11203,7 +11197,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B7" s="1">
         <v>15</v>
@@ -11232,7 +11226,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B8" s="1">
         <v>13</v>
@@ -11261,7 +11255,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B9" s="1">
         <v>10</v>
@@ -11299,51 +11293,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C1" t="s">
+        <v>570</v>
+      </c>
+      <c r="D1" t="s">
+        <v>571</v>
+      </c>
+      <c r="E1" t="s">
         <v>572</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>573</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>574</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>575</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>576</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>577</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>578</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>579</v>
-      </c>
-      <c r="K1" t="s">
-        <v>580</v>
-      </c>
-      <c r="L1" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C2" s="1">
-        <v>11.555648251813194</v>
+        <v>11.556294251698699</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -11375,13 +11369,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C3" s="1">
-        <v>11.08026246511187</v>
+        <v>11.080470160565543</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -11413,13 +11407,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B4" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C4" s="1">
-        <v>5.8059563107367413</v>
+        <v>5.8058265291582698</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -11451,13 +11445,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B5" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C5" s="1">
-        <v>5.1326764864572665</v>
+        <v>5.1329888132748298</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -11489,13 +11483,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B6" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C6" s="1">
-        <v>5.055755116928899</v>
+        <v>5.0563013930351088</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -11527,13 +11521,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C7" s="1">
-        <v>4.1950389570438817</v>
+        <v>4.1950336548328799</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -11565,13 +11559,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B8" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C8" s="1">
-        <v>3.5074137479836272</v>
+        <v>3.5074884104469102</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -11603,13 +11597,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B9" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C9" s="1">
-        <v>3.5058879772531526</v>
+        <v>3.5060299394785881</v>
       </c>
       <c r="D9" s="1">
         <v>8</v>
@@ -11641,13 +11635,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B10" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C10" s="1">
-        <v>2.9143975934326551</v>
+        <v>2.9144023478528807</v>
       </c>
       <c r="D10" s="1">
         <v>9</v>
@@ -11679,13 +11673,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B11" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C11" s="1">
-        <v>2.7840544617143244</v>
+        <v>2.7842509853544963</v>
       </c>
       <c r="D11" s="1">
         <v>10</v>
@@ -11717,13 +11711,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B12" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C12" s="1">
-        <v>2.7368028789218206</v>
+        <v>2.7377713612204535</v>
       </c>
       <c r="D12" s="1">
         <v>11</v>
@@ -11755,13 +11749,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B13" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C13" s="1">
-        <v>2.368713428897923</v>
+        <v>2.3683500662281531</v>
       </c>
       <c r="D13" s="1">
         <v>12</v>
@@ -11793,13 +11787,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C14" s="1">
-        <v>2.3277900736984605</v>
+        <v>2.3281098026431737</v>
       </c>
       <c r="D14" s="1">
         <v>13</v>
@@ -11831,13 +11825,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B15" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C15" s="1">
-        <v>2.3016561939632507</v>
+        <v>2.301604131552224</v>
       </c>
       <c r="D15" s="1">
         <v>14</v>
@@ -11869,13 +11863,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B16" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C16" s="1">
-        <v>1.7280500285695066</v>
+        <v>1.7278482502588635</v>
       </c>
       <c r="D16" s="1">
         <v>15</v>
@@ -11907,13 +11901,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B17" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C17" s="1">
-        <v>1.7170070853750834</v>
+        <v>1.7171733019023854</v>
       </c>
       <c r="D17" s="1">
         <v>16</v>
@@ -11945,13 +11939,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B18" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C18" s="1">
-        <v>1.5911404952949033</v>
+        <v>1.591216334973192</v>
       </c>
       <c r="D18" s="1">
         <v>17</v>
@@ -11983,13 +11977,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B19" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C19" s="1">
-        <v>1.4407456594950288</v>
+        <v>1.4409131008186427</v>
       </c>
       <c r="D19" s="1">
         <v>18</v>
@@ -12021,13 +12015,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B20" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C20" s="1">
-        <v>1.3256574972945001</v>
+        <v>1.325835178601309</v>
       </c>
       <c r="D20" s="1">
         <v>19</v>
@@ -12059,13 +12053,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B21" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C21" s="1">
-        <v>1.2845731910637455</v>
+        <v>1.284660256801095</v>
       </c>
       <c r="D21" s="1">
         <v>20</v>
@@ -12106,42 +12100,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C1" t="s">
+        <v>642</v>
+      </c>
+      <c r="D1" t="s">
+        <v>643</v>
+      </c>
+      <c r="E1" t="s">
         <v>644</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>645</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>646</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>647</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>648</v>
-      </c>
-      <c r="H1" t="s">
-        <v>649</v>
-      </c>
-      <c r="I1" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C2" s="1">
-        <v>1.7170070853750834</v>
+        <v>1.7171733019023854</v>
       </c>
       <c r="D2" s="1">
         <v>0.4551</v>
@@ -12159,18 +12153,18 @@
         <v>24989.876000000004</v>
       </c>
       <c r="I2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B3" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C3" s="1">
-        <v>11.555648251813194</v>
+        <v>11.556294251698699</v>
       </c>
       <c r="D3" s="1">
         <v>0.40150381944444441</v>
@@ -12188,18 +12182,18 @@
         <v>399049.57999999996</v>
       </c>
       <c r="I3" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B4" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C4" s="1">
-        <v>3.5058879772531526</v>
+        <v>3.5060299394785881</v>
       </c>
       <c r="D4" s="1">
         <v>0.38766428571428574</v>
@@ -12217,18 +12211,18 @@
         <v>33394.72199999998</v>
       </c>
       <c r="I4" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B5" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C5" s="1">
-        <v>0.27645197094336055</v>
+        <v>0.27646153165322279</v>
       </c>
       <c r="D5" s="1">
         <v>0.35620000000000002</v>
@@ -12246,18 +12240,18 @@
         <v>228450.54300000044</v>
       </c>
       <c r="I5" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B6" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C6" s="1">
-        <v>5.1326764864572665</v>
+        <v>5.1329888132748298</v>
       </c>
       <c r="D6" s="1">
         <v>0.35310833333333341</v>
@@ -12275,18 +12269,18 @@
         <v>78800.150999999983</v>
       </c>
       <c r="I6" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B7" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C7" s="1">
-        <v>5.055755116928899</v>
+        <v>5.0563013930351088</v>
       </c>
       <c r="D7" s="1">
         <v>0.35134900000000002</v>
@@ -12304,18 +12298,18 @@
         <v>62179.60000000002</v>
       </c>
       <c r="I7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B8" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C8" s="1">
-        <v>0.36925191643785826</v>
+        <v>0.36922974471185227</v>
       </c>
       <c r="D8" s="1">
         <v>0.30947142857142856</v>
@@ -12333,18 +12327,18 @@
         <v>202553.42199999993</v>
       </c>
       <c r="I8" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B9" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C9" s="1">
-        <v>0.46113373657562473</v>
+        <v>0.46113822164929857</v>
       </c>
       <c r="D9" s="1">
         <v>0.30681785714285709</v>
@@ -12362,21 +12356,21 @@
         <v>119072.14700000006</v>
       </c>
       <c r="I9" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B10" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C10" s="1">
-        <v>4.1950389570438817</v>
+        <v>4.1950336548328799</v>
       </c>
       <c r="D10" s="1">
-        <v>0.29911739130434783</v>
+        <v>0.29911739130434778</v>
       </c>
       <c r="E10" s="1">
         <v>9</v>
@@ -12391,18 +12385,18 @@
         <v>15873.213</v>
       </c>
       <c r="I10" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B11" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C11" s="1">
-        <v>11.08026246511187</v>
+        <v>11.080470160565543</v>
       </c>
       <c r="D11" s="1">
         <v>0.27601250000000005</v>
@@ -12420,18 +12414,18 @@
         <v>95941.227999999959</v>
       </c>
       <c r="I11" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B12" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C12" s="1">
-        <v>0.10807178032379773</v>
+        <v>0.1081084200597823</v>
       </c>
       <c r="D12" s="1">
         <v>1.8566038333333335</v>
@@ -12449,21 +12443,21 @@
         <v>254603.93300000016</v>
       </c>
       <c r="I12" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B13" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C13" s="1">
-        <v>1.3256574972945001</v>
+        <v>1.325835178601309</v>
       </c>
       <c r="D13" s="1">
-        <v>1.5244266285714299</v>
+        <v>1.5244266285714294</v>
       </c>
       <c r="E13" s="1">
         <v>26</v>
@@ -12478,21 +12472,21 @@
         <v>113443.51300000018</v>
       </c>
       <c r="I13" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B14" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C14" s="1">
-        <v>1.1890628033336259</v>
+        <v>1.1889398112694201</v>
       </c>
       <c r="D14" s="1">
-        <v>1.4219850161764702</v>
+        <v>1.4219850161764704</v>
       </c>
       <c r="E14" s="1">
         <v>24</v>
@@ -12507,18 +12501,18 @@
         <v>32779.104000000007</v>
       </c>
       <c r="I14" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B15" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C15" s="1">
-        <v>0.1030294646686056</v>
+        <v>0.10302593306737123</v>
       </c>
       <c r="D15" s="1">
         <v>1.4125695</v>
@@ -12536,21 +12530,21 @@
         <v>116290.70000000016</v>
       </c>
       <c r="I15" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B16" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C16" s="1">
-        <v>2.3277900736984605</v>
+        <v>2.3281098026431737</v>
       </c>
       <c r="D16" s="1">
-        <v>1.4009040241379305</v>
+        <v>1.4009040241379302</v>
       </c>
       <c r="E16" s="1">
         <v>16</v>
@@ -12565,21 +12559,21 @@
         <v>45714.238000000005</v>
       </c>
       <c r="I16" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B17" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C17" s="1">
-        <v>1.1504763137262528</v>
+        <v>1.1504232358256326</v>
       </c>
       <c r="D17" s="1">
-        <v>1.3664642666666666</v>
+        <v>1.3664642666666669</v>
       </c>
       <c r="E17" s="1">
         <v>19</v>
@@ -12594,18 +12588,18 @@
         <v>21793.239000000012</v>
       </c>
       <c r="I17" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B18" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C18" s="1">
-        <v>0.023734114749310063</v>
+        <v>0.023735222526769448</v>
       </c>
       <c r="D18" s="1">
         <v>1.3638920000000001</v>
@@ -12623,18 +12617,18 @@
         <v>40117.583999999981</v>
       </c>
       <c r="I18" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B19" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C19" s="1">
-        <v>0.36925191643785826</v>
+        <v>0.36922974471185227</v>
       </c>
       <c r="D19" s="1">
         <v>1.3091523571428572</v>
@@ -12652,18 +12646,18 @@
         <v>202553.42199999993</v>
       </c>
       <c r="I19" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B20" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C20" s="1">
-        <v>1.4407456594950288</v>
+        <v>1.4409131008186427</v>
       </c>
       <c r="D20" s="1">
         <v>1.2744417500000003</v>
@@ -12681,18 +12675,18 @@
         <v>8754.9249999999993</v>
       </c>
       <c r="I20" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B21" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C21" s="1">
-        <v>0.016997064090238212</v>
+        <v>0.016998066391718348</v>
       </c>
       <c r="D21" s="1">
         <v>1.2668966125000001</v>
@@ -12710,18 +12704,18 @@
         <v>85076.093000000023</v>
       </c>
       <c r="I21" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B22" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C22" s="1">
-        <v>1.7170070853750834</v>
+        <v>1.7171733019023854</v>
       </c>
       <c r="D22" s="1">
         <v>0.92336524171693335</v>
@@ -12739,18 +12733,18 @@
         <v>24989.876000000004</v>
       </c>
       <c r="I22" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B23" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C23" s="1">
-        <v>0.062208994824576438</v>
+        <v>0.062215626273110509</v>
       </c>
       <c r="D23" s="1">
         <v>0.83928571428571419</v>
@@ -12768,18 +12762,18 @@
         <v>706956.71799999836</v>
       </c>
       <c r="I23" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B24" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C24" s="1">
-        <v>11.555648251813194</v>
+        <v>11.556294251698699</v>
       </c>
       <c r="D24" s="1">
         <v>0.8089848312791772</v>
@@ -12797,18 +12791,18 @@
         <v>399049.57999999996</v>
       </c>
       <c r="I24" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B25" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C25" s="1">
-        <v>0.22816798567459234</v>
+        <v>0.22812275069214108</v>
       </c>
       <c r="D25" s="1">
         <v>0.80407463110951483</v>
@@ -12826,21 +12820,21 @@
         <v>826052.04600000288</v>
       </c>
       <c r="I25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B26" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C26" s="1">
-        <v>4.1950389570438817</v>
+        <v>4.1950336548328799</v>
       </c>
       <c r="D26" s="1">
-        <v>0.78679594367835848</v>
+        <v>0.78679594367835837</v>
       </c>
       <c r="E26" s="1">
         <v>9</v>
@@ -12855,18 +12849,18 @@
         <v>15873.213</v>
       </c>
       <c r="I26" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B27" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C27" s="1">
-        <v>0.27645197094336055</v>
+        <v>0.27646153165322279</v>
       </c>
       <c r="D27" s="1">
         <v>0.74880952380952381</v>
@@ -12884,18 +12878,18 @@
         <v>228450.54300000044</v>
       </c>
       <c r="I27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B28" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C28" s="1">
-        <v>5.1326764864572665</v>
+        <v>5.1329888132748298</v>
       </c>
       <c r="D28" s="1">
         <v>0.72302108457058967</v>
@@ -12913,18 +12907,18 @@
         <v>78800.150999999983</v>
       </c>
       <c r="I28" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B29" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C29" s="1">
-        <v>0.10807178032379773</v>
+        <v>0.1081084200597823</v>
       </c>
       <c r="D29" s="1">
         <v>0.71477455716586147</v>
@@ -12942,18 +12936,18 @@
         <v>254603.93300000016</v>
       </c>
       <c r="I29" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B30" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C30" s="1">
-        <v>11.08026246511187</v>
+        <v>11.080470160565543</v>
       </c>
       <c r="D30" s="1">
         <v>0.70823859229638986</v>
@@ -12971,18 +12965,18 @@
         <v>95941.227999999959</v>
       </c>
       <c r="I30" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B31" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C31" s="1">
-        <v>3.5058879772531526</v>
+        <v>3.5060299394785881</v>
       </c>
       <c r="D31" s="1">
         <v>0.69983176794676361</v>
@@ -13000,7 +12994,7 @@
         <v>33394.72199999998</v>
       </c>
       <c r="I31" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
   </sheetData>
